--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СКИМПРОТ ООД % ГРУПА 2/СКИМПРОТ ООД % ГРУПА 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СКИМПРОТ ООД % ГРУПА 2/СКИМПРОТ ООД % ГРУПА 2.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="СКИМПРОТ ООД % ГРУПА 2" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="97">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -73,6 +76,48 @@
     <t>2026-05-14</t>
   </si>
   <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-05-19</t>
+  </si>
+  <si>
+    <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>2026-05-22</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>2026-05-29</t>
+  </si>
+  <si>
+    <t>1101 София Ихтиман</t>
+  </si>
+  <si>
+    <t>1167 В. Търново вход</t>
+  </si>
+  <si>
+    <t>1901 София, Младост 4-ти км</t>
+  </si>
+  <si>
+    <t>1184 София Дружба2</t>
+  </si>
+  <si>
+    <t>1179 Русе, Липник</t>
+  </si>
+  <si>
+    <t>1198 Struma Highway</t>
+  </si>
+  <si>
     <t>СВ9234ВН</t>
   </si>
   <si>
@@ -115,31 +160,133 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>08:57</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>09:41</t>
-  </si>
-  <si>
-    <t>09:36</t>
-  </si>
-  <si>
-    <t>10:06</t>
-  </si>
-  <si>
-    <t>07:05</t>
-  </si>
-  <si>
-    <t>09:23</t>
-  </si>
-  <si>
-    <t>07:53</t>
-  </si>
-  <si>
-    <t>09:24</t>
+    <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>08:56:00</t>
+  </si>
+  <si>
+    <t>11:29:00</t>
+  </si>
+  <si>
+    <t>09:39:00</t>
+  </si>
+  <si>
+    <t>09:34:00</t>
+  </si>
+  <si>
+    <t>10:04:00</t>
+  </si>
+  <si>
+    <t>07:05:00</t>
+  </si>
+  <si>
+    <t>09:23:00</t>
+  </si>
+  <si>
+    <t>07:52:00</t>
+  </si>
+  <si>
+    <t>09:21:00</t>
+  </si>
+  <si>
+    <t>09:54:00</t>
+  </si>
+  <si>
+    <t>15:42:00</t>
+  </si>
+  <si>
+    <t>10:43:00</t>
+  </si>
+  <si>
+    <t>09:52:00</t>
+  </si>
+  <si>
+    <t>07:37:00</t>
+  </si>
+  <si>
+    <t>08:49:00</t>
+  </si>
+  <si>
+    <t>17:54:00</t>
+  </si>
+  <si>
+    <t>12:21:00</t>
+  </si>
+  <si>
+    <t>18:38:00</t>
+  </si>
+  <si>
+    <t>09:30:00</t>
+  </si>
+  <si>
+    <t>07:03:00</t>
+  </si>
+  <si>
+    <t>3231404852 3231404852</t>
+  </si>
+  <si>
+    <t>3231418112 3231418112</t>
+  </si>
+  <si>
+    <t>3231445358 3231445358</t>
+  </si>
+  <si>
+    <t>3231422758 3231422758</t>
+  </si>
+  <si>
+    <t>3231598796 3231598796</t>
+  </si>
+  <si>
+    <t>3231761668 3231761668</t>
+  </si>
+  <si>
+    <t>3231769424 3231769424</t>
+  </si>
+  <si>
+    <t>3231798554 3231798554</t>
+  </si>
+  <si>
+    <t>3231812317 3231812317</t>
+  </si>
+  <si>
+    <t>3231850413 3231850413</t>
+  </si>
+  <si>
+    <t>3232051605 3232051605</t>
+  </si>
+  <si>
+    <t>3232110014 3232110014</t>
+  </si>
+  <si>
+    <t>3232152013 3232152013</t>
+  </si>
+  <si>
+    <t>3232188351 3232188351</t>
+  </si>
+  <si>
+    <t>3232233108 3232233108</t>
+  </si>
+  <si>
+    <t>3232234019 3232234019</t>
+  </si>
+  <si>
+    <t>3232249330 3232249330</t>
+  </si>
+  <si>
+    <t>3232469207 3232469207</t>
+  </si>
+  <si>
+    <t>3232533256 3232533256</t>
+  </si>
+  <si>
+    <t>3232521172 3232521172</t>
+  </si>
+  <si>
+    <t>3232537651 3232537651</t>
   </si>
   <si>
     <t>Общи литри по продукт / СКИМПРОТ ООД % ГРУПА 2</t>
@@ -563,24 +710,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
-    <col min="5" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -620,508 +769,1133 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1101</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F2">
         <v>37.73</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2">
         <v>1.66</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>62.63</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.82</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>68.67</v>
       </c>
-      <c r="K2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
+      <c r="L2" t="s">
+        <v>50</v>
       </c>
       <c r="M2">
-        <v>152012</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>185440</v>
+      </c>
+      <c r="N2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3">
-        <v>1167</v>
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F3">
         <v>34.44</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H3">
         <v>1.66</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>57.17</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.8</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>61.99</v>
       </c>
-      <c r="K3" t="s">
-        <v>34</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
+      <c r="L3" t="s">
+        <v>51</v>
       </c>
       <c r="M3">
-        <v>134777</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4">
-        <v>1101</v>
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="F4">
         <v>40.58</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4">
         <v>0.84</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>34.09</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>0.84</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>34.09</v>
       </c>
-      <c r="K4" t="s">
-        <v>35</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
+      <c r="L4" t="s">
+        <v>52</v>
       </c>
       <c r="M4">
-        <v>261551</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5">
-        <v>1901</v>
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="F5">
         <v>36.4</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5">
         <v>0.83</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>30.21</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>0.83</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>30.21</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
+        <v>53</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
         <v>36</v>
       </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>207668</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6">
-        <v>1101</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="F6">
         <v>38.42</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6">
         <v>0.84</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>32.27</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>0.84</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>32.27</v>
       </c>
-      <c r="K6" t="s">
-        <v>37</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
+      <c r="L6" t="s">
+        <v>54</v>
       </c>
       <c r="M6">
-        <v>153122</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7">
-        <v>1101</v>
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F7">
         <v>48.88</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7">
         <v>1.65</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>80.65000000000001</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.81</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>88.47</v>
       </c>
-      <c r="K7" t="s">
-        <v>38</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
+      <c r="L7" t="s">
+        <v>55</v>
       </c>
       <c r="M7">
-        <v>154544</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8">
-        <v>1101</v>
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="F8">
         <v>40.96</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8">
         <v>0.83</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>34</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>0.83</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>34</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
+        <v>56</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9">
+        <v>39.3</v>
+      </c>
+      <c r="G9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9">
+        <v>0.82</v>
+      </c>
+      <c r="I9" s="1">
+        <v>32.23</v>
+      </c>
+      <c r="J9">
+        <v>0.82</v>
+      </c>
+      <c r="K9" s="1">
+        <v>32.23</v>
+      </c>
+      <c r="L9" t="s">
+        <v>56</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
         <v>39</v>
       </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>265229</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9">
-        <v>1101</v>
-      </c>
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10">
+        <v>40.28</v>
+      </c>
+      <c r="G10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10">
+        <v>1.65</v>
+      </c>
+      <c r="I10" s="1">
+        <v>66.45999999999999</v>
+      </c>
+      <c r="J10">
+        <v>1.8</v>
+      </c>
+      <c r="K10" s="1">
+        <v>72.5</v>
+      </c>
+      <c r="L10" t="s">
+        <v>57</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
         <v>30</v>
       </c>
-      <c r="E9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9">
-        <v>40.28</v>
-      </c>
-      <c r="G9" s="1">
-        <v>1.65</v>
-      </c>
-      <c r="H9">
-        <v>66.45999999999999</v>
-      </c>
-      <c r="I9" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="J9">
-        <v>72.5</v>
-      </c>
-      <c r="K9" t="s">
-        <v>40</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>265728</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10">
-        <v>1101</v>
-      </c>
-      <c r="C10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10">
-        <v>39.3</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0.82</v>
-      </c>
-      <c r="H10">
-        <v>32.23</v>
-      </c>
-      <c r="I10" s="1">
-        <v>0.82</v>
-      </c>
-      <c r="J10">
-        <v>32.23</v>
-      </c>
-      <c r="K10" t="s">
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" t="s">
         <v>41</v>
       </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>265786</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11">
-        <v>1901</v>
-      </c>
-      <c r="C11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" t="s">
-        <v>26</v>
-      </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F11">
         <v>42.4</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11">
         <v>1.65</v>
       </c>
-      <c r="H11">
+      <c r="I11" s="1">
         <v>69.95999999999999</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11">
         <v>1.77</v>
       </c>
-      <c r="J11">
+      <c r="K11" s="1">
         <v>75.05</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12">
+        <v>53.98</v>
+      </c>
+      <c r="G12" t="s">
+        <v>49</v>
+      </c>
+      <c r="H12">
+        <v>0.79</v>
+      </c>
+      <c r="I12" s="1">
+        <v>42.64</v>
+      </c>
+      <c r="J12">
+        <v>0.79</v>
+      </c>
+      <c r="K12" s="1">
+        <v>42.64</v>
+      </c>
+      <c r="L12" t="s">
+        <v>59</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13">
+        <v>33.89</v>
+      </c>
+      <c r="G13" t="s">
+        <v>49</v>
+      </c>
+      <c r="H13">
+        <v>0.79</v>
+      </c>
+      <c r="I13" s="1">
+        <v>26.77</v>
+      </c>
+      <c r="J13">
+        <v>0.79</v>
+      </c>
+      <c r="K13" s="1">
+        <v>26.77</v>
+      </c>
+      <c r="L13" t="s">
+        <v>60</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14">
+        <v>41.14</v>
+      </c>
+      <c r="G14" t="s">
+        <v>49</v>
+      </c>
+      <c r="H14">
+        <v>1.49</v>
+      </c>
+      <c r="I14" s="1">
+        <v>61.3</v>
+      </c>
+      <c r="J14">
+        <v>1.58</v>
+      </c>
+      <c r="K14" s="1">
+        <v>65</v>
+      </c>
+      <c r="L14" t="s">
+        <v>61</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15">
+        <v>49.7</v>
+      </c>
+      <c r="G15" t="s">
+        <v>49</v>
+      </c>
+      <c r="H15">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="I15" s="1">
+        <v>40.26</v>
+      </c>
+      <c r="J15">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K15" s="1">
+        <v>40.26</v>
+      </c>
+      <c r="L15" t="s">
+        <v>61</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16">
+        <v>31.3</v>
+      </c>
+      <c r="G16" t="s">
+        <v>49</v>
+      </c>
+      <c r="H16">
+        <v>0.79</v>
+      </c>
+      <c r="I16" s="1">
+        <v>24.73</v>
+      </c>
+      <c r="J16">
+        <v>0.79</v>
+      </c>
+      <c r="K16" s="1">
+        <v>24.73</v>
+      </c>
+      <c r="L16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" t="s">
         <v>39</v>
       </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>213546</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="3" t="s">
+      <c r="D17" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F17">
+        <v>37.92</v>
+      </c>
+      <c r="G17" t="s">
+        <v>49</v>
+      </c>
+      <c r="H17">
+        <v>1.63</v>
+      </c>
+      <c r="I17" s="1">
+        <v>61.81</v>
+      </c>
+      <c r="J17">
+        <v>1.77</v>
+      </c>
+      <c r="K17" s="1">
+        <v>67.12</v>
+      </c>
+      <c r="L17" t="s">
+        <v>63</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="4" t="s">
+      <c r="E18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18">
+        <v>40.09</v>
+      </c>
+      <c r="G18" t="s">
+        <v>49</v>
+      </c>
+      <c r="H18">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="I18" s="1">
+        <v>32.47</v>
+      </c>
+      <c r="J18">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K18" s="1">
+        <v>32.47</v>
+      </c>
+      <c r="L18" t="s">
+        <v>64</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="E19" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19">
+        <v>3.79</v>
+      </c>
+      <c r="G19" t="s">
+        <v>49</v>
+      </c>
+      <c r="H19">
+        <v>1.49</v>
+      </c>
+      <c r="I19" s="1">
+        <v>5.65</v>
+      </c>
+      <c r="J19">
+        <v>1.58</v>
+      </c>
+      <c r="K19" s="1">
+        <v>5.99</v>
+      </c>
+      <c r="L19" t="s">
+        <v>65</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20">
+        <v>25.06</v>
+      </c>
+      <c r="G20" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="I20" s="1">
+        <v>20.3</v>
+      </c>
+      <c r="J20">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K20" s="1">
+        <v>20.3</v>
+      </c>
+      <c r="L20" t="s">
+        <v>65</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21">
+        <v>25.97</v>
+      </c>
+      <c r="G21" t="s">
+        <v>49</v>
+      </c>
+      <c r="H21">
+        <v>0.77</v>
+      </c>
+      <c r="I21" s="1">
+        <v>20</v>
+      </c>
+      <c r="J21">
+        <v>0.77</v>
+      </c>
+      <c r="K21" s="1">
+        <v>20</v>
+      </c>
+      <c r="L21" t="s">
+        <v>66</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22">
+        <v>53.84</v>
+      </c>
+      <c r="G22" t="s">
+        <v>49</v>
+      </c>
+      <c r="H22">
+        <v>0.77</v>
+      </c>
+      <c r="I22" s="1">
+        <v>41.46</v>
+      </c>
+      <c r="J22">
+        <v>0.77</v>
+      </c>
+      <c r="K22" s="1">
+        <v>41.46</v>
+      </c>
+      <c r="L22" t="s">
+        <v>67</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" t="s">
+        <v>46</v>
+      </c>
+      <c r="F23">
+        <v>35.62</v>
+      </c>
+      <c r="G23" t="s">
+        <v>49</v>
+      </c>
+      <c r="H23">
+        <v>1.63</v>
+      </c>
+      <c r="I23" s="1">
+        <v>58.06</v>
+      </c>
+      <c r="J23">
+        <v>1.73</v>
+      </c>
+      <c r="K23" s="1">
+        <v>61.62</v>
+      </c>
+      <c r="L23" t="s">
+        <v>68</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="4" t="s">
+      <c r="E24" t="s">
         <v>46</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="6">
-        <v>203.73</v>
-      </c>
-      <c r="C16" s="6">
-        <v>5</v>
-      </c>
-      <c r="D16" s="7">
-        <v>1.6535</v>
-      </c>
-      <c r="E16" s="6">
-        <v>336.87</v>
-      </c>
-      <c r="F16" s="6">
-        <v>366.68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="6">
-        <v>195.66</v>
-      </c>
-      <c r="C17" s="6">
-        <v>5</v>
-      </c>
-      <c r="D17" s="7">
-        <v>0.8321</v>
-      </c>
-      <c r="E17" s="6">
-        <v>162.8</v>
-      </c>
-      <c r="F17" s="6">
-        <v>162.8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="8" t="s">
+      <c r="F24">
+        <v>39.66</v>
+      </c>
+      <c r="G24" t="s">
+        <v>49</v>
+      </c>
+      <c r="H24">
+        <v>1.62</v>
+      </c>
+      <c r="I24" s="1">
+        <v>64.25</v>
+      </c>
+      <c r="J24">
+        <v>1.74</v>
+      </c>
+      <c r="K24" s="1">
+        <v>69.01000000000001</v>
+      </c>
+      <c r="L24" t="s">
+        <v>69</v>
+      </c>
+      <c r="M24">
+        <v>207504</v>
+      </c>
+      <c r="N24" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="9">
-        <v>399.39</v>
-      </c>
-      <c r="C18" s="9">
-        <v>10</v>
-      </c>
-      <c r="D18" s="7"/>
-      <c r="E18" s="9">
-        <v>499.67</v>
-      </c>
-      <c r="F18" s="9">
-        <v>529.48</v>
+      <c r="B29" s="6">
+        <v>509.49</v>
+      </c>
+      <c r="C29" s="6">
+        <v>13</v>
+      </c>
+      <c r="D29" s="7">
+        <v>0.8075</v>
+      </c>
+      <c r="E29" s="6">
+        <v>411.43</v>
+      </c>
+      <c r="F29" s="6">
+        <v>411.43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="6">
+        <v>316.93</v>
+      </c>
+      <c r="C30" s="6">
+        <v>8</v>
+      </c>
+      <c r="D30" s="7">
+        <v>1.6439</v>
+      </c>
+      <c r="E30" s="6">
+        <v>520.99</v>
+      </c>
+      <c r="F30" s="6">
+        <v>564.4299999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" s="6">
+        <v>44.93</v>
+      </c>
+      <c r="C31" s="6">
+        <v>2</v>
+      </c>
+      <c r="D31" s="7">
+        <v>1.4901</v>
+      </c>
+      <c r="E31" s="6">
+        <v>66.95</v>
+      </c>
+      <c r="F31" s="6">
+        <v>70.98999999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" s="9">
+        <v>871.35</v>
+      </c>
+      <c r="C32" s="9">
+        <v>23</v>
+      </c>
+      <c r="D32" s="7"/>
+      <c r="E32" s="9">
+        <v>999.37</v>
+      </c>
+      <c r="F32" s="9">
+        <v>1046.85</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A27:F27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СКИМПРОТ ООД % ГРУПА 2/СКИМПРОТ ООД % ГРУПА 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СКИМПРОТ ООД % ГРУПА 2/СКИМПРОТ ООД % ГРУПА 2.xlsx
@@ -340,7 +340,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -350,12 +350,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -405,17 +399,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СКИМПРОТ ООД % ГРУПА 2/СКИМПРОТ ООД % ГРУПА 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СКИМПРОТ ООД % ГРУПА 2/СКИМПРОТ ООД % ГРУПА 2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="78">
   <si>
     <t>Дата</t>
   </si>
@@ -49,28 +49,187 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Километри</t>
-  </si>
-  <si>
-    <t>Billing_Document</t>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-06-02</t>
+  </si>
+  <si>
+    <t>2026-06-03</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
   </si>
   <si>
     <t>2026-06-10</t>
   </si>
   <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>2026-06-15</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-19</t>
+  </si>
+  <si>
+    <t>2026-06-23</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
     <t>Ихтиман</t>
   </si>
   <si>
+    <t>В.Търново</t>
+  </si>
+  <si>
+    <t>Търговище</t>
+  </si>
+  <si>
+    <t>София Дружба 2</t>
+  </si>
+  <si>
+    <t>Бургас езеро</t>
+  </si>
+  <si>
+    <t>София Младост</t>
+  </si>
+  <si>
+    <t>Тракия Езеро</t>
+  </si>
+  <si>
+    <t>СВ9234ВН</t>
+  </si>
+  <si>
+    <t>СВ6217СТ</t>
+  </si>
+  <si>
+    <t>СВ5410ХА</t>
+  </si>
+  <si>
+    <t>СВ0495СО</t>
+  </si>
+  <si>
+    <t>СВ5416КХ</t>
+  </si>
+  <si>
     <t>СА1823СМ</t>
   </si>
   <si>
+    <t>СВ5413КХ</t>
+  </si>
+  <si>
+    <t>78970153027721215</t>
+  </si>
+  <si>
+    <t>78970153027721058</t>
+  </si>
+  <si>
+    <t>78970153027721066</t>
+  </si>
+  <si>
+    <t>78970152027720136</t>
+  </si>
+  <si>
+    <t>78970153027721207</t>
+  </si>
+  <si>
     <t>78970155027722770</t>
   </si>
   <si>
+    <t>78970153027721199</t>
+  </si>
+  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>10:11</t>
+    <t>E GAS LPG</t>
+  </si>
+  <si>
+    <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
+    <t>2026-06-01 09:13:01</t>
+  </si>
+  <si>
+    <t>2026-06-01 10:00:56</t>
+  </si>
+  <si>
+    <t>2026-06-01 14:27:12</t>
+  </si>
+  <si>
+    <t>2026-06-02 06:40:53</t>
+  </si>
+  <si>
+    <t>2026-06-03 09:02:03</t>
+  </si>
+  <si>
+    <t>2026-06-03 17:05:50</t>
+  </si>
+  <si>
+    <t>2026-06-04 07:38:28</t>
+  </si>
+  <si>
+    <t>2026-06-04 10:23:43</t>
+  </si>
+  <si>
+    <t>2026-06-08 13:38:27</t>
+  </si>
+  <si>
+    <t>2026-06-08 13:38:28</t>
+  </si>
+  <si>
+    <t>2026-06-10 10:11:16</t>
+  </si>
+  <si>
+    <t>2026-06-11 09:32:02</t>
+  </si>
+  <si>
+    <t>2026-06-12 15:07:03</t>
+  </si>
+  <si>
+    <t>2026-06-14 07:04:21</t>
+  </si>
+  <si>
+    <t>2026-06-15 15:27:31</t>
+  </si>
+  <si>
+    <t>2026-06-17 07:45:10</t>
+  </si>
+  <si>
+    <t>2026-06-17 09:49:54</t>
+  </si>
+  <si>
+    <t>2026-06-17 10:27:30</t>
+  </si>
+  <si>
+    <t>2026-06-19 09:54:43</t>
+  </si>
+  <si>
+    <t>2026-06-23 09:54:43</t>
+  </si>
+  <si>
+    <t>2026-06-25 09:09:24</t>
+  </si>
+  <si>
+    <t>2026-06-25 09:13:08</t>
+  </si>
+  <si>
+    <t>2026-06-25 15:41:39</t>
   </si>
   <si>
     <t>Общи литри по продукт / СКИМПРОТ ООД % ГРУПА 2</t>
@@ -488,7 +647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -501,12 +660,10 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -540,125 +697,923 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="F2">
-        <v>13.12</v>
+        <v>34.8</v>
       </c>
       <c r="G2" s="1">
         <v>1.61</v>
       </c>
       <c r="H2">
-        <v>21.12</v>
+        <v>56.03</v>
       </c>
       <c r="I2" s="1">
+        <v>1.72</v>
+      </c>
+      <c r="J2">
+        <v>59.86</v>
+      </c>
+      <c r="K2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3">
+        <v>44.74</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.78</v>
+      </c>
+      <c r="H3">
+        <v>34.9</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.78</v>
+      </c>
+      <c r="J3">
+        <v>34.9</v>
+      </c>
+      <c r="K3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4">
+        <v>31.44</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.77</v>
+      </c>
+      <c r="H4">
+        <v>24.21</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.77</v>
+      </c>
+      <c r="J4">
+        <v>24.21</v>
+      </c>
+      <c r="K4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5">
+        <v>35.1</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="H5">
+        <v>56.16</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.72</v>
+      </c>
+      <c r="J5">
+        <v>60.37</v>
+      </c>
+      <c r="K5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6">
+        <v>35.82</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="H6">
+        <v>26.51</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="J6">
+        <v>26.51</v>
+      </c>
+      <c r="K6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7">
+        <v>46.98</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="H7">
+        <v>75.17</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.69</v>
+      </c>
+      <c r="J7">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="K7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8">
+        <v>38.33</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="H8">
+        <v>60.56</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1.72</v>
+      </c>
+      <c r="J8">
+        <v>65.93000000000001</v>
+      </c>
+      <c r="K8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9">
+        <v>29.49</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="H9">
+        <v>21.82</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="J9">
+        <v>21.82</v>
+      </c>
+      <c r="K9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10">
+        <v>43.96</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0.72</v>
+      </c>
+      <c r="H10">
+        <v>31.65</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0.72</v>
+      </c>
+      <c r="J10">
+        <v>31.65</v>
+      </c>
+      <c r="K10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11">
+        <v>37.18</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="H11">
+        <v>55.4</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J11">
+        <v>58</v>
+      </c>
+      <c r="K11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12">
+        <v>13.12</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="H12">
+        <v>20.34</v>
+      </c>
+      <c r="I12" s="1">
         <v>1.66</v>
       </c>
-      <c r="J2">
+      <c r="J12">
         <v>21.78</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13">
+        <v>41.28</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="H13">
+        <v>63.98</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1.65</v>
+      </c>
+      <c r="J13">
+        <v>68.11</v>
+      </c>
+      <c r="K13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
         <v>18</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>281742</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="3" t="s">
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14">
+        <v>42.24</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="H14">
+        <v>28.72</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="J14">
+        <v>28.72</v>
+      </c>
+      <c r="K14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="4" t="s">
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15">
+        <v>43.69</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="H15">
+        <v>67.72</v>
+      </c>
+      <c r="I15" s="1">
+        <v>1.63</v>
+      </c>
+      <c r="J15">
+        <v>71.20999999999999</v>
+      </c>
+      <c r="K15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16">
+        <v>26.97</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="H16">
+        <v>18.34</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="J16">
+        <v>18.34</v>
+      </c>
+      <c r="K16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F17">
+        <v>40.36</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="H17">
+        <v>62.15</v>
+      </c>
+      <c r="I17" s="1">
+        <v>1.63</v>
+      </c>
+      <c r="J17">
+        <v>65.79000000000001</v>
+      </c>
+      <c r="K17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" t="s">
+        <v>46</v>
+      </c>
+      <c r="F18">
+        <v>35.34</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="H18">
+        <v>54.42</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1.63</v>
+      </c>
+      <c r="J18">
+        <v>57.6</v>
+      </c>
+      <c r="K18" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19">
+        <v>46.85</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="H19">
+        <v>31.86</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="J19">
+        <v>31.86</v>
+      </c>
+      <c r="K19" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20">
+        <v>53</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="H20">
+        <v>34.98</v>
+      </c>
+      <c r="I20" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J20">
+        <v>34.98</v>
+      </c>
+      <c r="K20" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="B21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21">
+        <v>52.85</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="H21">
+        <v>34.88</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J21">
+        <v>34.88</v>
+      </c>
+      <c r="K21" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22">
+        <v>41.74</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="H22">
+        <v>27.55</v>
+      </c>
+      <c r="I22" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J22">
+        <v>27.55</v>
+      </c>
+      <c r="K22" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" t="s">
+        <v>46</v>
+      </c>
+      <c r="F23">
+        <v>39.82</v>
+      </c>
+      <c r="G23" s="1">
+        <v>1.46</v>
+      </c>
+      <c r="H23">
+        <v>58.14</v>
+      </c>
+      <c r="I23" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="J23">
+        <v>61.32</v>
+      </c>
+      <c r="K23" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" t="s">
+        <v>47</v>
+      </c>
+      <c r="F24">
+        <v>40.77</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="H24">
+        <v>26.91</v>
+      </c>
+      <c r="I24" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J24">
+        <v>26.91</v>
+      </c>
+      <c r="K24" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F28" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="6">
-        <v>13.12</v>
-      </c>
-      <c r="C7" s="6">
+    <row r="29" spans="1:11">
+      <c r="A29" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" s="6">
+        <v>489.87</v>
+      </c>
+      <c r="C29" s="6">
+        <v>12</v>
+      </c>
+      <c r="D29" s="7">
+        <v>0.6988</v>
+      </c>
+      <c r="E29" s="6">
+        <v>342.33</v>
+      </c>
+      <c r="F29" s="6">
+        <v>342.33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="6">
+        <v>368.82</v>
+      </c>
+      <c r="C30" s="6">
+        <v>10</v>
+      </c>
+      <c r="D30" s="7">
+        <v>1.5581</v>
+      </c>
+      <c r="E30" s="6">
+        <v>574.67</v>
+      </c>
+      <c r="F30" s="6">
+        <v>611.37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" s="6">
+        <v>37.18</v>
+      </c>
+      <c r="C31" s="6">
         <v>1</v>
       </c>
-      <c r="D7" s="7">
-        <v>1.6098</v>
-      </c>
-      <c r="E7" s="6">
-        <v>21.12</v>
-      </c>
-      <c r="F7" s="6">
-        <v>21.78</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="9">
-        <v>13.12</v>
-      </c>
-      <c r="C8" s="9">
-        <v>1</v>
-      </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="9">
-        <v>21.12</v>
-      </c>
-      <c r="F8" s="9">
-        <v>21.78</v>
+      <c r="D31" s="7">
+        <v>1.49</v>
+      </c>
+      <c r="E31" s="6">
+        <v>55.4</v>
+      </c>
+      <c r="F31" s="6">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B32" s="9">
+        <v>895.87</v>
+      </c>
+      <c r="C32" s="9">
+        <v>23</v>
+      </c>
+      <c r="D32" s="7"/>
+      <c r="E32" s="9">
+        <v>972.4</v>
+      </c>
+      <c r="F32" s="9">
+        <v>1011.7</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A27:F27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СКИМПРОТ ООД % ГРУПА 2/СКИМПРОТ ООД % ГРУПА 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СКИМПРОТ ООД % ГРУПА 2/СКИМПРОТ ООД % ГРУПА 2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="114">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,6 +52,12 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-01</t>
   </si>
   <si>
@@ -91,25 +100,37 @@
     <t>2026-06-25</t>
   </si>
   <si>
-    <t>Ихтиман</t>
-  </si>
-  <si>
-    <t>В.Търново</t>
-  </si>
-  <si>
-    <t>Търговище</t>
-  </si>
-  <si>
-    <t>София Дружба 2</t>
-  </si>
-  <si>
-    <t>Бургас езеро</t>
-  </si>
-  <si>
-    <t>София Младост</t>
-  </si>
-  <si>
-    <t>Тракия Езеро</t>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>1101 София Ихтиман</t>
+  </si>
+  <si>
+    <t>1103 Велико Търново изход</t>
+  </si>
+  <si>
+    <t>1184 София Дружба2</t>
+  </si>
+  <si>
+    <t>1918 O5 Търговище</t>
+  </si>
+  <si>
+    <t>1152 Бургас езеро</t>
+  </si>
+  <si>
+    <t>1901 София, Младост 4-ти км</t>
+  </si>
+  <si>
+    <t>1195 243 Тракия Езеро</t>
+  </si>
+  <si>
+    <t>1905 София, О5 Люлин</t>
   </si>
   <si>
     <t>СВ9234ВН</t>
@@ -163,73 +184,160 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-06-01 09:13:01</t>
-  </si>
-  <si>
-    <t>2026-06-01 10:00:56</t>
-  </si>
-  <si>
-    <t>2026-06-01 14:27:12</t>
-  </si>
-  <si>
-    <t>2026-06-02 06:40:53</t>
-  </si>
-  <si>
-    <t>2026-06-03 09:02:03</t>
-  </si>
-  <si>
-    <t>2026-06-03 17:05:50</t>
-  </si>
-  <si>
-    <t>2026-06-04 07:38:28</t>
-  </si>
-  <si>
-    <t>2026-06-04 10:23:43</t>
-  </si>
-  <si>
-    <t>2026-06-08 13:38:27</t>
-  </si>
-  <si>
-    <t>2026-06-08 13:38:28</t>
-  </si>
-  <si>
-    <t>2026-06-10 10:11:16</t>
-  </si>
-  <si>
-    <t>2026-06-11 09:32:02</t>
-  </si>
-  <si>
-    <t>2026-06-12 15:07:03</t>
-  </si>
-  <si>
-    <t>2026-06-14 07:04:21</t>
-  </si>
-  <si>
-    <t>2026-06-15 15:27:31</t>
-  </si>
-  <si>
-    <t>2026-06-17 07:45:10</t>
-  </si>
-  <si>
-    <t>2026-06-17 09:49:54</t>
-  </si>
-  <si>
-    <t>2026-06-17 10:27:30</t>
-  </si>
-  <si>
-    <t>2026-06-19 09:54:43</t>
-  </si>
-  <si>
-    <t>2026-06-23 09:54:43</t>
-  </si>
-  <si>
-    <t>2026-06-25 09:09:24</t>
-  </si>
-  <si>
-    <t>2026-06-25 09:13:08</t>
-  </si>
-  <si>
-    <t>2026-06-25 15:41:39</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>09:12:00</t>
+  </si>
+  <si>
+    <t>09:59:00</t>
+  </si>
+  <si>
+    <t>14:29:00</t>
+  </si>
+  <si>
+    <t>06:39:00</t>
+  </si>
+  <si>
+    <t>17:05:00</t>
+  </si>
+  <si>
+    <t>09:01:00</t>
+  </si>
+  <si>
+    <t>07:37:00</t>
+  </si>
+  <si>
+    <t>10:23:00</t>
+  </si>
+  <si>
+    <t>13:38:00</t>
+  </si>
+  <si>
+    <t>10:10:00</t>
+  </si>
+  <si>
+    <t>09:30:00</t>
+  </si>
+  <si>
+    <t>15:04:00</t>
+  </si>
+  <si>
+    <t>07:02:00</t>
+  </si>
+  <si>
+    <t>15:26:00</t>
+  </si>
+  <si>
+    <t>07:43:00</t>
+  </si>
+  <si>
+    <t>09:48:00</t>
+  </si>
+  <si>
+    <t>10:26:00</t>
+  </si>
+  <si>
+    <t>09:53:00</t>
+  </si>
+  <si>
+    <t>09:07:00</t>
+  </si>
+  <si>
+    <t>09:11:00</t>
+  </si>
+  <si>
+    <t>15:38:00</t>
+  </si>
+  <si>
+    <t>16:23:00</t>
+  </si>
+  <si>
+    <t>10:21:00</t>
+  </si>
+  <si>
+    <t>07:03:00</t>
+  </si>
+  <si>
+    <t>07:44:00</t>
+  </si>
+  <si>
+    <t>3232711044 3232711044</t>
+  </si>
+  <si>
+    <t>3232711821 3232711821</t>
+  </si>
+  <si>
+    <t>3232722446 3232722446</t>
+  </si>
+  <si>
+    <t>3232756518 3232756518</t>
+  </si>
+  <si>
+    <t>3232810192 3232810192</t>
+  </si>
+  <si>
+    <t>3232778970 3232778970</t>
+  </si>
+  <si>
+    <t>3232829033 3232829033</t>
+  </si>
+  <si>
+    <t>3232854744 3232854744</t>
+  </si>
+  <si>
+    <t>3233022860 3233022860</t>
+  </si>
+  <si>
+    <t>3233139366 3233139366</t>
+  </si>
+  <si>
+    <t>3233147229 3233147229</t>
+  </si>
+  <si>
+    <t>3233220537 3233220537</t>
+  </si>
+  <si>
+    <t>3233336063 3233336063</t>
+  </si>
+  <si>
+    <t>3233392533 3233392533</t>
+  </si>
+  <si>
+    <t>3233456086 3233456086</t>
+  </si>
+  <si>
+    <t>3233477135 3233477135</t>
+  </si>
+  <si>
+    <t>3233477807 3233477807</t>
+  </si>
+  <si>
+    <t>3233574620 3233574620</t>
+  </si>
+  <si>
+    <t>3233755889 3233755889</t>
+  </si>
+  <si>
+    <t>3233830982 3233830982</t>
+  </si>
+  <si>
+    <t>3233831896 3233831896</t>
+  </si>
+  <si>
+    <t>3233856820 3233856820</t>
+  </si>
+  <si>
+    <t>3233935264 3233935264</t>
+  </si>
+  <si>
+    <t>3234046965 3234046965</t>
+  </si>
+  <si>
+    <t>3234081895 3234081895</t>
+  </si>
+  <si>
+    <t>3234095509 3234095509</t>
   </si>
   <si>
     <t>Общи литри по продукт / СКИМПРОТ ООД % ГРУПА 2</t>
@@ -647,7 +755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -656,14 +764,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -697,923 +808,1359 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F2">
         <v>34.8</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H2">
         <v>1.61</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>56.03</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.72</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>59.86</v>
       </c>
-      <c r="K2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F3">
         <v>44.74</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H3">
         <v>0.78</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>34.9</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>0.78</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>34.9</v>
       </c>
-      <c r="K3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F4">
         <v>31.44</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4">
         <v>0.77</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>24.21</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>0.77</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>24.21</v>
       </c>
-      <c r="K4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" t="s">
+        <v>59</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F5">
         <v>35.1</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5">
         <v>1.6</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>56.16</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.72</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>60.37</v>
       </c>
-      <c r="K5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" t="s">
+        <v>60</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6">
+        <v>46.98</v>
+      </c>
+      <c r="G6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H6">
+        <v>1.6</v>
+      </c>
+      <c r="I6" s="1">
+        <v>75.17</v>
+      </c>
+      <c r="J6">
+        <v>1.69</v>
+      </c>
+      <c r="K6" s="1">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="L6" t="s">
+        <v>61</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
         <v>34</v>
       </c>
-      <c r="D6" t="s">
+      <c r="C7" t="s">
         <v>41</v>
       </c>
-      <c r="E6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6">
+      <c r="D7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7">
         <v>35.82</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H7">
         <v>0.74</v>
       </c>
-      <c r="H6">
+      <c r="I7" s="1">
         <v>26.51</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J7">
         <v>0.74</v>
       </c>
-      <c r="J6">
+      <c r="K7" s="1">
         <v>26.51</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L7" t="s">
+        <v>62</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7">
-        <v>46.98</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="H7">
-        <v>75.17</v>
-      </c>
-      <c r="I7" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="J7">
-        <v>79.40000000000001</v>
-      </c>
-      <c r="K7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" t="s">
-        <v>46</v>
       </c>
       <c r="F8">
         <v>38.33</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8">
         <v>1.58</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>60.56</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.72</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>65.93000000000001</v>
       </c>
-      <c r="K8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F9">
         <v>29.49</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9">
         <v>0.74</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="1">
         <v>21.82</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>0.74</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>21.82</v>
       </c>
-      <c r="K9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L9" t="s">
+        <v>64</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10">
+        <v>37.18</v>
+      </c>
+      <c r="G10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10">
+        <v>1.49</v>
+      </c>
+      <c r="I10" s="1">
+        <v>55.4</v>
+      </c>
+      <c r="J10">
+        <v>1.56</v>
+      </c>
+      <c r="K10" s="1">
+        <v>58</v>
+      </c>
+      <c r="L10" t="s">
+        <v>65</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s">
         <v>41</v>
       </c>
-      <c r="E10" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10">
+      <c r="D11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11">
         <v>43.96</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G11" t="s">
+        <v>56</v>
+      </c>
+      <c r="H11">
         <v>0.72</v>
       </c>
-      <c r="H10">
+      <c r="I11" s="1">
         <v>31.65</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J11">
         <v>0.72</v>
       </c>
-      <c r="J10">
+      <c r="K11" s="1">
         <v>31.65</v>
       </c>
-      <c r="K10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11">
-        <v>37.18</v>
-      </c>
-      <c r="G11" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="H11">
-        <v>55.4</v>
-      </c>
-      <c r="I11" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J11">
-        <v>58</v>
-      </c>
-      <c r="K11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="L11" t="s">
+        <v>65</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F12">
         <v>13.12</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" t="s">
+        <v>56</v>
+      </c>
+      <c r="H12">
         <v>1.55</v>
       </c>
-      <c r="H12">
+      <c r="I12" s="1">
         <v>20.34</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12">
         <v>1.66</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="1">
         <v>21.78</v>
       </c>
-      <c r="K12" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="L12" t="s">
+        <v>66</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E13" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F13">
         <v>41.28</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" t="s">
+        <v>56</v>
+      </c>
+      <c r="H13">
         <v>1.55</v>
       </c>
-      <c r="H13">
+      <c r="I13" s="1">
         <v>63.98</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13">
         <v>1.65</v>
       </c>
-      <c r="J13">
+      <c r="K13" s="1">
         <v>68.11</v>
       </c>
-      <c r="K13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="L13" t="s">
+        <v>67</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E14" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F14">
-        <v>42.24</v>
-      </c>
-      <c r="G14" s="1">
+        <v>42.23</v>
+      </c>
+      <c r="G14" t="s">
+        <v>56</v>
+      </c>
+      <c r="H14">
         <v>0.68</v>
       </c>
-      <c r="H14">
+      <c r="I14" s="1">
         <v>28.72</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14">
         <v>0.68</v>
       </c>
-      <c r="J14">
+      <c r="K14" s="1">
         <v>28.72</v>
       </c>
-      <c r="K14" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="L14" t="s">
+        <v>68</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E15" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F15">
         <v>43.69</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" t="s">
+        <v>56</v>
+      </c>
+      <c r="H15">
         <v>1.55</v>
       </c>
-      <c r="H15">
+      <c r="I15" s="1">
         <v>67.72</v>
       </c>
-      <c r="I15" s="1">
+      <c r="J15">
         <v>1.63</v>
       </c>
-      <c r="J15">
+      <c r="K15" s="1">
         <v>71.20999999999999</v>
       </c>
-      <c r="K15" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="L15" t="s">
+        <v>69</v>
+      </c>
+      <c r="M15">
+        <v>208030</v>
+      </c>
+      <c r="N15" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D16" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E16" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F16">
         <v>26.97</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" t="s">
+        <v>56</v>
+      </c>
+      <c r="H16">
         <v>0.68</v>
       </c>
-      <c r="H16">
+      <c r="I16" s="1">
         <v>18.34</v>
       </c>
-      <c r="I16" s="1">
+      <c r="J16">
         <v>0.68</v>
       </c>
-      <c r="J16">
+      <c r="K16" s="1">
         <v>18.34</v>
       </c>
-      <c r="K16" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="L16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D17" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="E17" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F17">
         <v>40.36</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" t="s">
+        <v>56</v>
+      </c>
+      <c r="H17">
         <v>1.54</v>
       </c>
-      <c r="H17">
+      <c r="I17" s="1">
         <v>62.15</v>
       </c>
-      <c r="I17" s="1">
+      <c r="J17">
         <v>1.63</v>
       </c>
-      <c r="J17">
+      <c r="K17" s="1">
         <v>65.79000000000001</v>
       </c>
-      <c r="K17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="L17" t="s">
+        <v>71</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D18" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E18" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F18">
         <v>35.34</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" t="s">
+        <v>56</v>
+      </c>
+      <c r="H18">
         <v>1.54</v>
       </c>
-      <c r="H18">
+      <c r="I18" s="1">
         <v>54.42</v>
       </c>
-      <c r="I18" s="1">
+      <c r="J18">
         <v>1.63</v>
       </c>
-      <c r="J18">
+      <c r="K18" s="1">
         <v>57.6</v>
       </c>
-      <c r="K18" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="L18" t="s">
+        <v>72</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D19" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E19" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F19">
         <v>46.85</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" t="s">
+        <v>56</v>
+      </c>
+      <c r="H19">
         <v>0.68</v>
       </c>
-      <c r="H19">
+      <c r="I19" s="1">
         <v>31.86</v>
       </c>
-      <c r="I19" s="1">
+      <c r="J19">
         <v>0.68</v>
       </c>
-      <c r="J19">
+      <c r="K19" s="1">
         <v>31.86</v>
       </c>
-      <c r="K19" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="L19" t="s">
+        <v>73</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C20" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D20" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E20" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F20">
         <v>53</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20" t="s">
+        <v>56</v>
+      </c>
+      <c r="H20">
         <v>0.66</v>
       </c>
-      <c r="H20">
+      <c r="I20" s="1">
         <v>34.98</v>
       </c>
-      <c r="I20" s="1">
+      <c r="J20">
         <v>0.66</v>
       </c>
-      <c r="J20">
+      <c r="K20" s="1">
         <v>34.98</v>
       </c>
-      <c r="K20" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="L20" t="s">
+        <v>74</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C21" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D21" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F21">
         <v>52.85</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G21" t="s">
+        <v>56</v>
+      </c>
+      <c r="H21">
         <v>0.66</v>
       </c>
-      <c r="H21">
+      <c r="I21" s="1">
         <v>34.88</v>
       </c>
-      <c r="I21" s="1">
+      <c r="J21">
         <v>0.66</v>
       </c>
-      <c r="J21">
+      <c r="K21" s="1">
         <v>34.88</v>
       </c>
-      <c r="K21" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+      <c r="L21" t="s">
+        <v>74</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D22" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E22" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F22">
         <v>41.74</v>
       </c>
-      <c r="G22" s="1">
+      <c r="G22" t="s">
+        <v>56</v>
+      </c>
+      <c r="H22">
         <v>0.66</v>
       </c>
-      <c r="H22">
+      <c r="I22" s="1">
         <v>27.55</v>
       </c>
-      <c r="I22" s="1">
+      <c r="J22">
         <v>0.66</v>
       </c>
-      <c r="J22">
+      <c r="K22" s="1">
         <v>27.55</v>
       </c>
-      <c r="K22" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+      <c r="L22" t="s">
+        <v>75</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C23" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D23" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E23" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F23">
         <v>39.82</v>
       </c>
-      <c r="G23" s="1">
+      <c r="G23" t="s">
+        <v>56</v>
+      </c>
+      <c r="H23">
         <v>1.46</v>
       </c>
-      <c r="H23">
+      <c r="I23" s="1">
         <v>58.14</v>
       </c>
-      <c r="I23" s="1">
+      <c r="J23">
         <v>1.54</v>
       </c>
-      <c r="J23">
+      <c r="K23" s="1">
         <v>61.32</v>
       </c>
-      <c r="K23" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+      <c r="L23" t="s">
+        <v>76</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D24" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E24" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F24">
         <v>40.77</v>
       </c>
-      <c r="G24" s="1">
+      <c r="G24" t="s">
+        <v>56</v>
+      </c>
+      <c r="H24">
         <v>0.66</v>
       </c>
-      <c r="H24">
+      <c r="I24" s="1">
         <v>26.91</v>
       </c>
-      <c r="I24" s="1">
+      <c r="J24">
         <v>0.66</v>
       </c>
-      <c r="J24">
+      <c r="K24" s="1">
         <v>26.91</v>
       </c>
-      <c r="K24" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29" s="5" t="s">
+      <c r="L24" t="s">
+        <v>77</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" t="s">
         <v>47</v>
       </c>
-      <c r="B29" s="6">
-        <v>489.87</v>
-      </c>
-      <c r="C29" s="6">
+      <c r="E25" t="s">
+        <v>54</v>
+      </c>
+      <c r="F25">
+        <v>27.58</v>
+      </c>
+      <c r="G25" t="s">
+        <v>56</v>
+      </c>
+      <c r="H25">
+        <v>0.66</v>
+      </c>
+      <c r="I25" s="1">
+        <v>18.2</v>
+      </c>
+      <c r="J25">
+        <v>0.66</v>
+      </c>
+      <c r="K25" s="1">
+        <v>18.2</v>
+      </c>
+      <c r="L25" t="s">
+        <v>78</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" t="s">
+        <v>47</v>
+      </c>
+      <c r="E26" t="s">
+        <v>55</v>
+      </c>
+      <c r="F26">
+        <v>30.13</v>
+      </c>
+      <c r="G26" t="s">
+        <v>56</v>
+      </c>
+      <c r="H26">
+        <v>1.39</v>
+      </c>
+      <c r="I26" s="1">
+        <v>41.88</v>
+      </c>
+      <c r="J26">
+        <v>1.51</v>
+      </c>
+      <c r="K26" s="1">
+        <v>45.5</v>
+      </c>
+      <c r="L26" t="s">
+        <v>79</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" t="s">
+        <v>47</v>
+      </c>
+      <c r="E27" t="s">
+        <v>54</v>
+      </c>
+      <c r="F27">
+        <v>52.2</v>
+      </c>
+      <c r="G27" t="s">
+        <v>56</v>
+      </c>
+      <c r="H27">
+        <v>0.66</v>
+      </c>
+      <c r="I27" s="1">
+        <v>34.45</v>
+      </c>
+      <c r="J27">
+        <v>0.66</v>
+      </c>
+      <c r="K27" s="1">
+        <v>34.45</v>
+      </c>
+      <c r="L27" t="s">
+        <v>79</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" t="s">
+        <v>45</v>
+      </c>
+      <c r="D28" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" t="s">
+        <v>53</v>
+      </c>
+      <c r="F28">
+        <v>43.7</v>
+      </c>
+      <c r="G28" t="s">
+        <v>56</v>
+      </c>
+      <c r="H28">
+        <v>1.43</v>
+      </c>
+      <c r="I28" s="1">
+        <v>62.49</v>
+      </c>
+      <c r="J28">
+        <v>1.54</v>
+      </c>
+      <c r="K28" s="1">
+        <v>67.3</v>
+      </c>
+      <c r="L28" t="s">
+        <v>80</v>
+      </c>
+      <c r="M28">
+        <v>208860</v>
+      </c>
+      <c r="N28" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" t="s">
+        <v>50</v>
+      </c>
+      <c r="E29" t="s">
+        <v>53</v>
+      </c>
+      <c r="F29">
+        <v>39.5</v>
+      </c>
+      <c r="G29" t="s">
+        <v>56</v>
+      </c>
+      <c r="H29">
+        <v>1.43</v>
+      </c>
+      <c r="I29" s="1">
+        <v>56.48</v>
+      </c>
+      <c r="J29">
+        <v>1.54</v>
+      </c>
+      <c r="K29" s="1">
+        <v>60.83</v>
+      </c>
+      <c r="L29" t="s">
+        <v>81</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" s="6">
+        <v>569.64</v>
+      </c>
+      <c r="C34" s="6">
+        <v>14</v>
+      </c>
+      <c r="D34" s="7">
+        <v>0.6934</v>
+      </c>
+      <c r="E34" s="6">
+        <v>394.98</v>
+      </c>
+      <c r="F34" s="6">
+        <v>394.98</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" s="6">
+        <v>452.02</v>
+      </c>
+      <c r="C35" s="6">
         <v>12</v>
       </c>
-      <c r="D29" s="7">
-        <v>0.6988</v>
-      </c>
-      <c r="E29" s="6">
-        <v>342.33</v>
-      </c>
-      <c r="F29" s="6">
-        <v>342.33</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="A30" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B30" s="6">
-        <v>368.82</v>
-      </c>
-      <c r="C30" s="6">
-        <v>10</v>
-      </c>
-      <c r="D30" s="7">
-        <v>1.5581</v>
-      </c>
-      <c r="E30" s="6">
-        <v>574.67</v>
-      </c>
-      <c r="F30" s="6">
-        <v>611.37</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="A31" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B31" s="6">
-        <v>37.18</v>
-      </c>
-      <c r="C31" s="6">
-        <v>1</v>
-      </c>
-      <c r="D31" s="7">
-        <v>1.49</v>
-      </c>
-      <c r="E31" s="6">
-        <v>55.4</v>
-      </c>
-      <c r="F31" s="6">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
-      <c r="A32" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="B32" s="9">
-        <v>895.87</v>
-      </c>
-      <c r="C32" s="9">
-        <v>23</v>
-      </c>
-      <c r="D32" s="7"/>
-      <c r="E32" s="9">
-        <v>972.4</v>
-      </c>
-      <c r="F32" s="9">
-        <v>1011.7</v>
+      <c r="D35" s="7">
+        <v>1.5345</v>
+      </c>
+      <c r="E35" s="6">
+        <v>693.64</v>
+      </c>
+      <c r="F35" s="6">
+        <v>739.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" s="6">
+        <v>67.31</v>
+      </c>
+      <c r="C36" s="6">
+        <v>2</v>
+      </c>
+      <c r="D36" s="7">
+        <v>1.4453</v>
+      </c>
+      <c r="E36" s="6">
+        <v>97.28</v>
+      </c>
+      <c r="F36" s="6">
+        <v>103.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B37" s="9">
+        <v>1088.97</v>
+      </c>
+      <c r="C37" s="9">
+        <v>28</v>
+      </c>
+      <c r="D37" s="7"/>
+      <c r="E37" s="9">
+        <v>1185.9</v>
+      </c>
+      <c r="F37" s="9">
+        <v>1237.98</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A32:F32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СКИМПРОТ ООД % ГРУПА 2/СКИМПРОТ ООД % ГРУПА 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СКИМПРОТ ООД % ГРУПА 2/СКИМПРОТ ООД % ГРУПА 2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="114">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-01</t>
   </si>
   <si>
@@ -82,13 +88,49 @@
     <t>2026-07-15</t>
   </si>
   <si>
-    <t>Ихтиман</t>
-  </si>
-  <si>
-    <t>София Малинов</t>
-  </si>
-  <si>
-    <t>София Дружба 2</t>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>1101 София Ихтиман</t>
+  </si>
+  <si>
+    <t>1192 София, Младост Ал. Малинов</t>
+  </si>
+  <si>
+    <t>1184 София Дружба2</t>
+  </si>
+  <si>
+    <t>1901 София, Младост 4-ти км</t>
+  </si>
+  <si>
+    <t>1162 София Люлин П. Владигеров</t>
   </si>
   <si>
     <t>СВ5410ХА</t>
@@ -106,6 +148,12 @@
     <t>СВ9234ВН</t>
   </si>
   <si>
+    <t>СВ5413КХ</t>
+  </si>
+  <si>
+    <t>СА1823СМ</t>
+  </si>
+  <si>
     <t>78970153027721066</t>
   </si>
   <si>
@@ -121,49 +169,175 @@
     <t>78970153027721215</t>
   </si>
   <si>
+    <t>78970153027721199</t>
+  </si>
+  <si>
+    <t>78970155027722770</t>
+  </si>
+  <si>
     <t>E GAS LPG</t>
   </si>
   <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-07-01 09:33:00</t>
-  </si>
-  <si>
-    <t>2026-07-01 11:11:04</t>
-  </si>
-  <si>
-    <t>2026-07-03 10:17:20</t>
-  </si>
-  <si>
-    <t>2026-07-06 09:11:02</t>
-  </si>
-  <si>
-    <t>2026-07-07 09:12:57</t>
-  </si>
-  <si>
-    <t>2026-07-07 13:33:43</t>
-  </si>
-  <si>
-    <t>2026-07-08 08:40:16</t>
-  </si>
-  <si>
-    <t>2026-07-09 07:37:55</t>
-  </si>
-  <si>
-    <t>2026-07-10 09:39:57</t>
-  </si>
-  <si>
-    <t>2026-07-13 09:16:02</t>
-  </si>
-  <si>
-    <t>2026-07-13 09:32:41</t>
-  </si>
-  <si>
-    <t>2026-07-14 09:20:33</t>
-  </si>
-  <si>
-    <t>2026-07-15 10:44:42</t>
+    <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>09:32:00</t>
+  </si>
+  <si>
+    <t>11:10:00</t>
+  </si>
+  <si>
+    <t>10:16:00</t>
+  </si>
+  <si>
+    <t>09:10:00</t>
+  </si>
+  <si>
+    <t>09:12:00</t>
+  </si>
+  <si>
+    <t>13:34:00</t>
+  </si>
+  <si>
+    <t>08:39:00</t>
+  </si>
+  <si>
+    <t>07:37:00</t>
+  </si>
+  <si>
+    <t>09:39:00</t>
+  </si>
+  <si>
+    <t>09:15:00</t>
+  </si>
+  <si>
+    <t>09:19:00</t>
+  </si>
+  <si>
+    <t>10:44:00</t>
+  </si>
+  <si>
+    <t>11:01:00</t>
+  </si>
+  <si>
+    <t>11:07:00</t>
+  </si>
+  <si>
+    <t>06:43:00</t>
+  </si>
+  <si>
+    <t>18:42:00</t>
+  </si>
+  <si>
+    <t>07:02:00</t>
+  </si>
+  <si>
+    <t>13:50:00</t>
+  </si>
+  <si>
+    <t>10:38:00</t>
+  </si>
+  <si>
+    <t>10:31:00</t>
+  </si>
+  <si>
+    <t>11:08:00</t>
+  </si>
+  <si>
+    <t>07:46:00</t>
+  </si>
+  <si>
+    <t>11:42:00</t>
+  </si>
+  <si>
+    <t>09:24:00</t>
+  </si>
+  <si>
+    <t>17:55:00</t>
+  </si>
+  <si>
+    <t>3234149626 3234149626</t>
+  </si>
+  <si>
+    <t>3234152207 3234152207</t>
+  </si>
+  <si>
+    <t>3234246224 3234246224</t>
+  </si>
+  <si>
+    <t>3234393317 3234393317</t>
+  </si>
+  <si>
+    <t>3234436106 3234436106</t>
+  </si>
+  <si>
+    <t>3234443222 3234443222</t>
+  </si>
+  <si>
+    <t>3234464570 3234464570</t>
+  </si>
+  <si>
+    <t>3234488943 3234488943</t>
+  </si>
+  <si>
+    <t>3234607062 3234607062</t>
+  </si>
+  <si>
+    <t>3234734548 3234734548</t>
+  </si>
+  <si>
+    <t>3234735812 3234735812</t>
+  </si>
+  <si>
+    <t>3234782282 3234782282</t>
+  </si>
+  <si>
+    <t>3234831941 3234831941</t>
+  </si>
+  <si>
+    <t>3234883750 3234883750</t>
+  </si>
+  <si>
+    <t>3234937615 3234937615</t>
+  </si>
+  <si>
+    <t>3235117055 3235117055</t>
+  </si>
+  <si>
+    <t>3235203931 3235203931</t>
+  </si>
+  <si>
+    <t>3235231023 3235231023</t>
+  </si>
+  <si>
+    <t>3235242544 3235242544</t>
+  </si>
+  <si>
+    <t>3235283370 3235283370</t>
+  </si>
+  <si>
+    <t>3235429527 3235429527</t>
+  </si>
+  <si>
+    <t>3235526246 3235526246</t>
+  </si>
+  <si>
+    <t>3235554981 3235554981</t>
+  </si>
+  <si>
+    <t>3235579774 3235579774</t>
+  </si>
+  <si>
+    <t>3235605767 3235605767</t>
+  </si>
+  <si>
+    <t>3235633661 3235633661</t>
   </si>
   <si>
     <t>Общи литри по продукт / СКИМПРОТ ООД % ГРУПА 2</t>
@@ -581,7 +755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -590,15 +764,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -635,592 +811,1312 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="F2">
         <v>26.36</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H2">
         <v>0.66</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>17.4</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>0.66</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>17.4</v>
       </c>
-      <c r="K2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="L2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="F3">
         <v>39.85</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H3">
         <v>0.66</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>26.3</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>0.66</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>26.3</v>
       </c>
-      <c r="K3" t="s">
-        <v>38</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="L3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="F4">
         <v>52.57</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4">
         <v>0.65</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>34.17</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>0.65</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>34.17</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>59</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
         <v>39</v>
       </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="F5">
         <v>47.46</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5">
         <v>0.63</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>29.9</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>0.63</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>29.9</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
+        <v>60</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
         <v>40</v>
       </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="F6">
         <v>41.81</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H6">
         <v>0.63</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>26.34</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>0.63</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>26.34</v>
       </c>
-      <c r="K6" t="s">
-        <v>41</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="L6" t="s">
+        <v>61</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="F7">
         <v>42.13</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H7">
         <v>0.63</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>26.54</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>0.63</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>26.54</v>
       </c>
-      <c r="K7" t="s">
-        <v>42</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="L7" t="s">
+        <v>62</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="F8">
         <v>37.71</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8">
         <v>1.44</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>54.3</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.55</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>58.45</v>
       </c>
-      <c r="K8" t="s">
-        <v>43</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="L8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="F9">
         <v>38.95</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9">
         <v>1.44</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="1">
         <v>56.09</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>1.55</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>60.37</v>
       </c>
-      <c r="K9" t="s">
-        <v>44</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="L9" t="s">
+        <v>64</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="F10">
         <v>44.29</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10">
         <v>0.63</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="1">
         <v>27.9</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>0.63</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>27.9</v>
       </c>
-      <c r="K10" t="s">
-        <v>45</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="L10" t="s">
+        <v>65</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11">
+        <v>38.91</v>
+      </c>
+      <c r="G11" t="s">
+        <v>56</v>
+      </c>
+      <c r="H11">
+        <v>1.48</v>
+      </c>
+      <c r="I11" s="1">
+        <v>57.59</v>
+      </c>
+      <c r="J11">
+        <v>1.58</v>
+      </c>
+      <c r="K11" s="1">
+        <v>61.48</v>
+      </c>
+      <c r="L11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M11">
+        <v>187547</v>
+      </c>
+      <c r="N11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12">
+        <v>29.98</v>
+      </c>
+      <c r="G12" t="s">
+        <v>56</v>
+      </c>
+      <c r="H12">
+        <v>1.48</v>
+      </c>
+      <c r="I12" s="1">
+        <v>44.37</v>
+      </c>
+      <c r="J12">
+        <v>1.58</v>
+      </c>
+      <c r="K12" s="1">
+        <v>47.37</v>
+      </c>
+      <c r="L12" t="s">
+        <v>66</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
         <v>22</v>
       </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11">
-        <v>29.98</v>
-      </c>
-      <c r="G11" s="1">
-        <v>1.48</v>
-      </c>
-      <c r="H11">
-        <v>44.37</v>
-      </c>
-      <c r="I11" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="J11">
-        <v>47.37</v>
-      </c>
-      <c r="K11" t="s">
-        <v>46</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="B13" t="s">
         <v>34</v>
       </c>
-      <c r="E12" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12">
-        <v>38.91</v>
-      </c>
-      <c r="G12" s="1">
-        <v>1.48</v>
-      </c>
-      <c r="H12">
-        <v>57.59</v>
-      </c>
-      <c r="I12" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="J12">
-        <v>61.48</v>
-      </c>
-      <c r="K12" t="s">
+      <c r="C13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" t="s">
         <v>47</v>
       </c>
-      <c r="L12">
-        <v>187547</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" t="s">
-        <v>31</v>
-      </c>
       <c r="E13" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="F13">
         <v>39.78</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" t="s">
+        <v>56</v>
+      </c>
+      <c r="H13">
         <v>0.63</v>
       </c>
-      <c r="H13">
+      <c r="I13" s="1">
         <v>25.06</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13">
         <v>0.63</v>
       </c>
-      <c r="J13">
+      <c r="K13" s="1">
         <v>25.06</v>
       </c>
-      <c r="K13" t="s">
-        <v>48</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+      <c r="L13" t="s">
+        <v>67</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E14" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="F14">
         <v>36.89</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" t="s">
+        <v>56</v>
+      </c>
+      <c r="H14">
         <v>0.63</v>
       </c>
-      <c r="H14">
+      <c r="I14" s="1">
         <v>23.24</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14">
         <v>0.63</v>
       </c>
-      <c r="J14">
+      <c r="K14" s="1">
         <v>23.24</v>
       </c>
-      <c r="K14" t="s">
+      <c r="L14" t="s">
+        <v>68</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15">
+        <v>41.85</v>
+      </c>
+      <c r="G15" t="s">
+        <v>56</v>
+      </c>
+      <c r="H15">
+        <v>1.53</v>
+      </c>
+      <c r="I15" s="1">
+        <v>64.03</v>
+      </c>
+      <c r="J15">
+        <v>1.62</v>
+      </c>
+      <c r="K15" s="1">
+        <v>67.8</v>
+      </c>
+      <c r="L15" t="s">
+        <v>69</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16">
+        <v>26.14</v>
+      </c>
+      <c r="G16" t="s">
+        <v>56</v>
+      </c>
+      <c r="H16">
+        <v>1.4</v>
+      </c>
+      <c r="I16" s="1">
+        <v>36.6</v>
+      </c>
+      <c r="J16">
+        <v>1.53</v>
+      </c>
+      <c r="K16" s="1">
+        <v>39.99</v>
+      </c>
+      <c r="L16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17">
+        <v>53.48</v>
+      </c>
+      <c r="G17" t="s">
+        <v>56</v>
+      </c>
+      <c r="H17">
+        <v>0.64</v>
+      </c>
+      <c r="I17" s="1">
+        <v>34.23</v>
+      </c>
+      <c r="J17">
+        <v>0.64</v>
+      </c>
+      <c r="K17" s="1">
+        <v>34.23</v>
+      </c>
+      <c r="L17" t="s">
+        <v>70</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" t="s">
         <v>49</v>
       </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="4" t="s">
+      <c r="E18" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18">
+        <v>41.83</v>
+      </c>
+      <c r="G18" t="s">
+        <v>56</v>
+      </c>
+      <c r="H18">
+        <v>1.59</v>
+      </c>
+      <c r="I18" s="1">
+        <v>66.51000000000001</v>
+      </c>
+      <c r="J18">
+        <v>1.7</v>
+      </c>
+      <c r="K18" s="1">
+        <v>71.11</v>
+      </c>
+      <c r="L18" t="s">
+        <v>71</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19">
+        <v>40.27</v>
+      </c>
+      <c r="G19" t="s">
+        <v>56</v>
+      </c>
+      <c r="H19">
+        <v>0.64</v>
+      </c>
+      <c r="I19" s="1">
+        <v>25.77</v>
+      </c>
+      <c r="J19">
+        <v>0.64</v>
+      </c>
+      <c r="K19" s="1">
+        <v>25.77</v>
+      </c>
+      <c r="L19" t="s">
+        <v>72</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="E20" t="s">
+        <v>54</v>
+      </c>
+      <c r="F20">
+        <v>46.51</v>
+      </c>
+      <c r="G20" t="s">
+        <v>56</v>
+      </c>
+      <c r="H20">
+        <v>1.62</v>
+      </c>
+      <c r="I20" s="1">
+        <v>75.34999999999999</v>
+      </c>
+      <c r="J20">
+        <v>1.72</v>
+      </c>
+      <c r="K20" s="1">
+        <v>80</v>
+      </c>
+      <c r="L20" t="s">
+        <v>73</v>
+      </c>
+      <c r="M20">
+        <v>209590</v>
+      </c>
+      <c r="N20" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21">
+        <v>42.25</v>
+      </c>
+      <c r="G21" t="s">
+        <v>56</v>
+      </c>
+      <c r="H21">
+        <v>0.64</v>
+      </c>
+      <c r="I21" s="1">
+        <v>27.04</v>
+      </c>
+      <c r="J21">
+        <v>0.64</v>
+      </c>
+      <c r="K21" s="1">
+        <v>27.04</v>
+      </c>
+      <c r="L21" t="s">
+        <v>74</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="E22" t="s">
+        <v>54</v>
+      </c>
+      <c r="F22">
+        <v>35.58</v>
+      </c>
+      <c r="G22" t="s">
+        <v>56</v>
+      </c>
+      <c r="H22">
+        <v>1.65</v>
+      </c>
+      <c r="I22" s="1">
+        <v>58.71</v>
+      </c>
+      <c r="J22">
+        <v>1.74</v>
+      </c>
+      <c r="K22" s="1">
+        <v>61.91</v>
+      </c>
+      <c r="L22" t="s">
+        <v>75</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E23" t="s">
         <v>53</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="F23">
+        <v>53.05</v>
+      </c>
+      <c r="G23" t="s">
+        <v>56</v>
+      </c>
+      <c r="H23">
+        <v>0.64</v>
+      </c>
+      <c r="I23" s="1">
+        <v>33.95</v>
+      </c>
+      <c r="J23">
+        <v>0.64</v>
+      </c>
+      <c r="K23" s="1">
+        <v>33.95</v>
+      </c>
+      <c r="L23" t="s">
+        <v>76</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" t="s">
+        <v>47</v>
+      </c>
+      <c r="E24" t="s">
+        <v>53</v>
+      </c>
+      <c r="F24">
+        <v>45.48</v>
+      </c>
+      <c r="G24" t="s">
+        <v>56</v>
+      </c>
+      <c r="H24">
+        <v>0.64</v>
+      </c>
+      <c r="I24" s="1">
+        <v>29.11</v>
+      </c>
+      <c r="J24">
+        <v>0.64</v>
+      </c>
+      <c r="K24" s="1">
+        <v>29.11</v>
+      </c>
+      <c r="L24" t="s">
+        <v>77</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" t="s">
+        <v>49</v>
+      </c>
+      <c r="E25" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="6">
-        <v>371.14</v>
-      </c>
-      <c r="C19" s="6">
-        <v>9</v>
-      </c>
-      <c r="D19" s="7">
-        <v>0.6382</v>
-      </c>
-      <c r="E19" s="6">
-        <v>236.85</v>
-      </c>
-      <c r="F19" s="6">
-        <v>236.85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="6">
-        <v>145.55</v>
-      </c>
-      <c r="C20" s="6">
-        <v>4</v>
-      </c>
-      <c r="D20" s="7">
-        <v>1.4589</v>
-      </c>
-      <c r="E20" s="6">
-        <v>212.35</v>
-      </c>
-      <c r="F20" s="6">
-        <v>227.67</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="8" t="s">
+      <c r="F25">
+        <v>42.18</v>
+      </c>
+      <c r="G25" t="s">
+        <v>56</v>
+      </c>
+      <c r="H25">
+        <v>1.7</v>
+      </c>
+      <c r="I25" s="1">
+        <v>71.70999999999999</v>
+      </c>
+      <c r="J25">
+        <v>1.78</v>
+      </c>
+      <c r="K25" s="1">
+        <v>75.08</v>
+      </c>
+      <c r="L25" t="s">
+        <v>78</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" t="s">
+        <v>54</v>
+      </c>
+      <c r="F26">
+        <v>41.4</v>
+      </c>
+      <c r="G26" t="s">
+        <v>56</v>
+      </c>
+      <c r="H26">
+        <v>1.7</v>
+      </c>
+      <c r="I26" s="1">
+        <v>70.38</v>
+      </c>
+      <c r="J26">
+        <v>1.77</v>
+      </c>
+      <c r="K26" s="1">
+        <v>73.28</v>
+      </c>
+      <c r="L26" t="s">
+        <v>79</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" t="s">
+        <v>39</v>
+      </c>
+      <c r="D27" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27" t="s">
+        <v>53</v>
+      </c>
+      <c r="F27">
+        <v>43.73</v>
+      </c>
+      <c r="G27" t="s">
+        <v>56</v>
+      </c>
+      <c r="H27">
+        <v>0.64</v>
+      </c>
+      <c r="I27" s="1">
+        <v>27.99</v>
+      </c>
+      <c r="J27">
+        <v>0.64</v>
+      </c>
+      <c r="K27" s="1">
+        <v>27.99</v>
+      </c>
+      <c r="L27" t="s">
+        <v>80</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" t="s">
+        <v>47</v>
+      </c>
+      <c r="E28" t="s">
+        <v>53</v>
+      </c>
+      <c r="F28">
+        <v>48.27</v>
+      </c>
+      <c r="G28" t="s">
+        <v>56</v>
+      </c>
+      <c r="H28">
+        <v>0.64</v>
+      </c>
+      <c r="I28" s="1">
+        <v>30.89</v>
+      </c>
+      <c r="J28">
+        <v>0.64</v>
+      </c>
+      <c r="K28" s="1">
+        <v>30.89</v>
+      </c>
+      <c r="L28" t="s">
+        <v>81</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" s="6">
+        <v>697.67</v>
+      </c>
+      <c r="C33" s="6">
+        <v>16</v>
+      </c>
+      <c r="D33" s="7">
+        <v>0.639</v>
+      </c>
+      <c r="E33" s="6">
+        <v>445.83</v>
+      </c>
+      <c r="F33" s="6">
+        <v>445.83</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" s="6">
+        <v>394.9</v>
+      </c>
+      <c r="C34" s="6">
+        <v>10</v>
+      </c>
+      <c r="D34" s="7">
+        <v>1.5676</v>
+      </c>
+      <c r="E34" s="6">
+        <v>619.04</v>
+      </c>
+      <c r="F34" s="6">
+        <v>656.85</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B21" s="9">
-        <v>516.6900000000001</v>
-      </c>
-      <c r="C21" s="9">
-        <v>13</v>
-      </c>
-      <c r="D21" s="7"/>
-      <c r="E21" s="9">
-        <v>449.2</v>
-      </c>
-      <c r="F21" s="9">
-        <v>464.52</v>
+      <c r="B35" s="6">
+        <v>26.14</v>
+      </c>
+      <c r="C35" s="6">
+        <v>1</v>
+      </c>
+      <c r="D35" s="7">
+        <v>1.4002</v>
+      </c>
+      <c r="E35" s="6">
+        <v>36.6</v>
+      </c>
+      <c r="F35" s="6">
+        <v>39.99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B36" s="9">
+        <v>1118.71</v>
+      </c>
+      <c r="C36" s="9">
+        <v>27</v>
+      </c>
+      <c r="D36" s="7"/>
+      <c r="E36" s="9">
+        <v>1101.47</v>
+      </c>
+      <c r="F36" s="9">
+        <v>1142.67</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A31:F31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СКИМПРОТ ООД % ГРУПА 2/СКИМПРОТ ООД % ГРУПА 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СКИМПРОТ ООД % ГРУПА 2/СКИМПРОТ ООД % ГРУПА 2.xlsx
@@ -364,7 +364,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -2047,7 +2047,7 @@
         <v>16</v>
       </c>
       <c r="D33" s="7">
-        <v>0.639</v>
+        <v>0.639027</v>
       </c>
       <c r="E33" s="6">
         <v>445.83</v>
@@ -2067,7 +2067,7 @@
         <v>10</v>
       </c>
       <c r="D34" s="7">
-        <v>1.5676</v>
+        <v>1.567587</v>
       </c>
       <c r="E34" s="6">
         <v>619.04</v>
@@ -2087,7 +2087,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="7">
-        <v>1.4002</v>
+        <v>1.400153</v>
       </c>
       <c r="E35" s="6">
         <v>36.6</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СКИМПРОТ ООД % ГРУПА 2/СКИМПРОТ ООД % ГРУПА 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СКИМПРОТ ООД % ГРУПА 2/СКИМПРОТ ООД % ГРУПА 2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="115">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -755,7 +758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -768,13 +771,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -817,1198 +820,1282 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F2">
-        <v>26.36</v>
+        <v>26.364</v>
       </c>
       <c r="G2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H2">
         <v>0.66</v>
       </c>
       <c r="I2" s="1">
-        <v>17.4</v>
+        <v>0.66</v>
       </c>
       <c r="J2">
+        <v>17.40024</v>
+      </c>
+      <c r="K2" s="1">
         <v>0.66</v>
       </c>
-      <c r="K2" s="1">
-        <v>17.4</v>
-      </c>
-      <c r="L2" t="s">
-        <v>57</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="L2" s="1">
+        <v>17.40024</v>
+      </c>
+      <c r="M2" t="s">
+        <v>58</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F3">
-        <v>39.85</v>
+        <v>39.848</v>
       </c>
       <c r="G3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H3">
         <v>0.66</v>
       </c>
       <c r="I3" s="1">
-        <v>26.3</v>
+        <v>0.66</v>
       </c>
       <c r="J3">
+        <v>26.29968</v>
+      </c>
+      <c r="K3" s="1">
         <v>0.66</v>
       </c>
-      <c r="K3" s="1">
-        <v>26.3</v>
-      </c>
-      <c r="L3" t="s">
-        <v>58</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="L3" s="1">
+        <v>26.29968</v>
+      </c>
+      <c r="M3" t="s">
+        <v>59</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F4">
-        <v>52.57</v>
+        <v>52.569</v>
       </c>
       <c r="G4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H4">
         <v>0.65</v>
       </c>
       <c r="I4" s="1">
-        <v>34.17</v>
+        <v>0.65</v>
       </c>
       <c r="J4">
+        <v>34.16985</v>
+      </c>
+      <c r="K4" s="1">
         <v>0.65</v>
       </c>
-      <c r="K4" s="1">
-        <v>34.17</v>
-      </c>
-      <c r="L4" t="s">
-        <v>59</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="L4" s="1">
+        <v>34.16985</v>
+      </c>
+      <c r="M4" t="s">
+        <v>60</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F5">
         <v>47.46</v>
       </c>
       <c r="G5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H5">
         <v>0.63</v>
       </c>
       <c r="I5" s="1">
-        <v>29.9</v>
+        <v>0.63</v>
       </c>
       <c r="J5">
+        <v>29.8998</v>
+      </c>
+      <c r="K5" s="1">
         <v>0.63</v>
       </c>
-      <c r="K5" s="1">
-        <v>29.9</v>
-      </c>
-      <c r="L5" t="s">
-        <v>60</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="L5" s="1">
+        <v>29.8998</v>
+      </c>
+      <c r="M5" t="s">
+        <v>61</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F6">
         <v>41.81</v>
       </c>
       <c r="G6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H6">
         <v>0.63</v>
       </c>
       <c r="I6" s="1">
-        <v>26.34</v>
+        <v>0.63</v>
       </c>
       <c r="J6">
+        <v>26.3403</v>
+      </c>
+      <c r="K6" s="1">
         <v>0.63</v>
       </c>
-      <c r="K6" s="1">
-        <v>26.34</v>
-      </c>
-      <c r="L6" t="s">
-        <v>61</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="L6" s="1">
+        <v>26.3403</v>
+      </c>
+      <c r="M6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F7">
-        <v>42.13</v>
+        <v>42.127</v>
       </c>
       <c r="G7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H7">
         <v>0.63</v>
       </c>
       <c r="I7" s="1">
-        <v>26.54</v>
+        <v>0.63</v>
       </c>
       <c r="J7">
+        <v>26.54001</v>
+      </c>
+      <c r="K7" s="1">
         <v>0.63</v>
       </c>
-      <c r="K7" s="1">
-        <v>26.54</v>
-      </c>
-      <c r="L7" t="s">
-        <v>62</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="L7" s="1">
+        <v>26.54001</v>
+      </c>
+      <c r="M7" t="s">
+        <v>63</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F8">
         <v>37.71</v>
       </c>
       <c r="G8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H8">
-        <v>1.44</v>
+        <v>1.412</v>
       </c>
       <c r="I8" s="1">
-        <v>54.3</v>
+        <v>1.442</v>
       </c>
       <c r="J8">
+        <v>54.37782</v>
+      </c>
+      <c r="K8" s="1">
         <v>1.55</v>
       </c>
-      <c r="K8" s="1">
-        <v>58.45</v>
-      </c>
-      <c r="L8" t="s">
-        <v>63</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="L8" s="1">
+        <v>58.4505</v>
+      </c>
+      <c r="M8" t="s">
+        <v>64</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9">
+        <v>38.948</v>
+      </c>
+      <c r="G9" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9">
+        <v>1.412</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1.442</v>
+      </c>
+      <c r="J9">
+        <v>56.163016</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="L9" s="1">
+        <v>60.3694</v>
+      </c>
+      <c r="M9" t="s">
+        <v>65</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" t="s">
         <v>54</v>
       </c>
-      <c r="F9">
-        <v>38.95</v>
-      </c>
-      <c r="G9" t="s">
-        <v>56</v>
-      </c>
-      <c r="H9">
-        <v>1.44</v>
-      </c>
-      <c r="I9" s="1">
-        <v>56.09</v>
-      </c>
-      <c r="J9">
-        <v>1.55</v>
-      </c>
-      <c r="K9" s="1">
-        <v>60.37</v>
-      </c>
-      <c r="L9" t="s">
-        <v>64</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" t="s">
-        <v>53</v>
-      </c>
       <c r="F10">
-        <v>44.29</v>
+        <v>44.286</v>
       </c>
       <c r="G10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H10">
         <v>0.63</v>
       </c>
       <c r="I10" s="1">
-        <v>27.9</v>
+        <v>0.63</v>
       </c>
       <c r="J10">
+        <v>27.90018</v>
+      </c>
+      <c r="K10" s="1">
         <v>0.63</v>
       </c>
-      <c r="K10" s="1">
-        <v>27.9</v>
-      </c>
-      <c r="L10" t="s">
-        <v>65</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="L10" s="1">
+        <v>27.90018</v>
+      </c>
+      <c r="M10" t="s">
+        <v>66</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11">
+        <v>38.911</v>
+      </c>
+      <c r="G11" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11">
+        <v>1.451</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1.481</v>
+      </c>
+      <c r="J11">
+        <v>57.627191</v>
+      </c>
+      <c r="K11" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="L11" s="1">
+        <v>61.47938</v>
+      </c>
+      <c r="M11" t="s">
+        <v>58</v>
+      </c>
+      <c r="N11">
+        <v>187547</v>
+      </c>
+      <c r="O11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12">
+        <v>29.981</v>
+      </c>
+      <c r="G12" t="s">
+        <v>57</v>
+      </c>
+      <c r="H12">
+        <v>1.451</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1.481</v>
+      </c>
+      <c r="J12">
+        <v>44.401861</v>
+      </c>
+      <c r="K12" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="L12" s="1">
+        <v>47.36998</v>
+      </c>
+      <c r="M12" t="s">
+        <v>67</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" t="s">
         <v>54</v>
       </c>
-      <c r="F11">
-        <v>38.91</v>
-      </c>
-      <c r="G11" t="s">
-        <v>56</v>
-      </c>
-      <c r="H11">
-        <v>1.48</v>
-      </c>
-      <c r="I11" s="1">
-        <v>57.59</v>
-      </c>
-      <c r="J11">
-        <v>1.58</v>
-      </c>
-      <c r="K11" s="1">
-        <v>61.48</v>
-      </c>
-      <c r="L11" t="s">
-        <v>57</v>
-      </c>
-      <c r="M11">
-        <v>187547</v>
-      </c>
-      <c r="N11" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" t="s">
-        <v>54</v>
-      </c>
-      <c r="F12">
-        <v>29.98</v>
-      </c>
-      <c r="G12" t="s">
-        <v>56</v>
-      </c>
-      <c r="H12">
-        <v>1.48</v>
-      </c>
-      <c r="I12" s="1">
-        <v>44.37</v>
-      </c>
-      <c r="J12">
-        <v>1.58</v>
-      </c>
-      <c r="K12" s="1">
-        <v>47.37</v>
-      </c>
-      <c r="L12" t="s">
-        <v>66</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" t="s">
-        <v>53</v>
-      </c>
       <c r="F13">
-        <v>39.78</v>
+        <v>39.778</v>
       </c>
       <c r="G13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H13">
         <v>0.63</v>
       </c>
       <c r="I13" s="1">
-        <v>25.06</v>
+        <v>0.63</v>
       </c>
       <c r="J13">
+        <v>25.06014</v>
+      </c>
+      <c r="K13" s="1">
         <v>0.63</v>
       </c>
-      <c r="K13" s="1">
-        <v>25.06</v>
-      </c>
-      <c r="L13" t="s">
-        <v>67</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="L13" s="1">
+        <v>25.06014</v>
+      </c>
+      <c r="M13" t="s">
+        <v>68</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F14">
-        <v>36.89</v>
+        <v>36.889</v>
       </c>
       <c r="G14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H14">
         <v>0.63</v>
       </c>
       <c r="I14" s="1">
-        <v>23.24</v>
+        <v>0.63</v>
       </c>
       <c r="J14">
+        <v>23.24007</v>
+      </c>
+      <c r="K14" s="1">
         <v>0.63</v>
       </c>
-      <c r="K14" s="1">
-        <v>23.24</v>
-      </c>
-      <c r="L14" t="s">
-        <v>68</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="L14" s="1">
+        <v>23.24007</v>
+      </c>
+      <c r="M14" t="s">
+        <v>69</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15">
+        <v>41.852</v>
+      </c>
+      <c r="G15" t="s">
+        <v>57</v>
+      </c>
+      <c r="H15">
+        <v>1.499</v>
+      </c>
+      <c r="I15" s="1">
+        <v>1.529</v>
+      </c>
+      <c r="J15">
+        <v>63.991708</v>
+      </c>
+      <c r="K15" s="1">
+        <v>1.62</v>
+      </c>
+      <c r="L15" s="1">
+        <v>67.80024</v>
+      </c>
+      <c r="M15" t="s">
+        <v>70</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
         <v>41</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D16" t="s">
         <v>48</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E16" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16">
+        <v>26.137</v>
+      </c>
+      <c r="G16" t="s">
+        <v>57</v>
+      </c>
+      <c r="H16">
+        <v>1.369</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1.399</v>
+      </c>
+      <c r="J16">
+        <v>36.565663</v>
+      </c>
+      <c r="K16" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="L16" s="1">
+        <v>39.98961</v>
+      </c>
+      <c r="M16" t="s">
+        <v>71</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" t="s">
         <v>54</v>
       </c>
-      <c r="F15">
-        <v>41.85</v>
-      </c>
-      <c r="G15" t="s">
-        <v>56</v>
-      </c>
-      <c r="H15">
-        <v>1.53</v>
-      </c>
-      <c r="I15" s="1">
-        <v>64.03</v>
-      </c>
-      <c r="J15">
-        <v>1.62</v>
-      </c>
-      <c r="K15" s="1">
-        <v>67.8</v>
-      </c>
-      <c r="L15" t="s">
-        <v>69</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" t="s">
-        <v>47</v>
-      </c>
-      <c r="E16" t="s">
-        <v>55</v>
-      </c>
-      <c r="F16">
-        <v>26.14</v>
-      </c>
-      <c r="G16" t="s">
-        <v>56</v>
-      </c>
-      <c r="H16">
-        <v>1.4</v>
-      </c>
-      <c r="I16" s="1">
-        <v>36.6</v>
-      </c>
-      <c r="J16">
-        <v>1.53</v>
-      </c>
-      <c r="K16" s="1">
-        <v>39.99</v>
-      </c>
-      <c r="L16" t="s">
-        <v>70</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17" t="s">
-        <v>47</v>
-      </c>
-      <c r="E17" t="s">
-        <v>53</v>
-      </c>
       <c r="F17">
-        <v>53.48</v>
+        <v>53.484</v>
       </c>
       <c r="G17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H17">
         <v>0.64</v>
       </c>
       <c r="I17" s="1">
-        <v>34.23</v>
+        <v>0.64</v>
       </c>
       <c r="J17">
+        <v>34.22976</v>
+      </c>
+      <c r="K17" s="1">
         <v>0.64</v>
       </c>
-      <c r="K17" s="1">
-        <v>34.23</v>
-      </c>
-      <c r="L17" t="s">
-        <v>70</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="L17" s="1">
+        <v>34.22976</v>
+      </c>
+      <c r="M17" t="s">
+        <v>71</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E18" t="s">
+        <v>55</v>
+      </c>
+      <c r="F18">
+        <v>41.829</v>
+      </c>
+      <c r="G18" t="s">
+        <v>57</v>
+      </c>
+      <c r="H18">
+        <v>1.564</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1.594</v>
+      </c>
+      <c r="J18">
+        <v>66.675426</v>
+      </c>
+      <c r="K18" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="L18" s="1">
+        <v>71.1093</v>
+      </c>
+      <c r="M18" t="s">
+        <v>72</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" t="s">
         <v>54</v>
       </c>
-      <c r="F18">
-        <v>41.83</v>
-      </c>
-      <c r="G18" t="s">
-        <v>56</v>
-      </c>
-      <c r="H18">
-        <v>1.59</v>
-      </c>
-      <c r="I18" s="1">
-        <v>66.51000000000001</v>
-      </c>
-      <c r="J18">
-        <v>1.7</v>
-      </c>
-      <c r="K18" s="1">
-        <v>71.11</v>
-      </c>
-      <c r="L18" t="s">
-        <v>71</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" t="s">
-        <v>40</v>
-      </c>
-      <c r="D19" t="s">
-        <v>47</v>
-      </c>
-      <c r="E19" t="s">
-        <v>53</v>
-      </c>
       <c r="F19">
-        <v>40.27</v>
+        <v>40.266</v>
       </c>
       <c r="G19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H19">
         <v>0.64</v>
       </c>
       <c r="I19" s="1">
-        <v>25.77</v>
+        <v>0.64</v>
       </c>
       <c r="J19">
+        <v>25.77024</v>
+      </c>
+      <c r="K19" s="1">
         <v>0.64</v>
       </c>
-      <c r="K19" s="1">
-        <v>25.77</v>
-      </c>
-      <c r="L19" t="s">
-        <v>72</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="L19" s="1">
+        <v>25.77024</v>
+      </c>
+      <c r="M19" t="s">
+        <v>73</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E20" t="s">
+        <v>55</v>
+      </c>
+      <c r="F20">
+        <v>46.512</v>
+      </c>
+      <c r="G20" t="s">
+        <v>57</v>
+      </c>
+      <c r="H20">
+        <v>1.588</v>
+      </c>
+      <c r="I20" s="1">
+        <v>1.618</v>
+      </c>
+      <c r="J20">
+        <v>75.256416</v>
+      </c>
+      <c r="K20" s="1">
+        <v>1.72</v>
+      </c>
+      <c r="L20" s="1">
+        <v>80.00064</v>
+      </c>
+      <c r="M20" t="s">
+        <v>74</v>
+      </c>
+      <c r="N20">
+        <v>209590</v>
+      </c>
+      <c r="O20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" t="s">
         <v>54</v>
-      </c>
-      <c r="F20">
-        <v>46.51</v>
-      </c>
-      <c r="G20" t="s">
-        <v>56</v>
-      </c>
-      <c r="H20">
-        <v>1.62</v>
-      </c>
-      <c r="I20" s="1">
-        <v>75.34999999999999</v>
-      </c>
-      <c r="J20">
-        <v>1.72</v>
-      </c>
-      <c r="K20" s="1">
-        <v>80</v>
-      </c>
-      <c r="L20" t="s">
-        <v>73</v>
-      </c>
-      <c r="M20">
-        <v>209590</v>
-      </c>
-      <c r="N20" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" t="s">
-        <v>46</v>
-      </c>
-      <c r="E21" t="s">
-        <v>53</v>
       </c>
       <c r="F21">
         <v>42.25</v>
       </c>
       <c r="G21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H21">
         <v>0.64</v>
       </c>
       <c r="I21" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="J21">
         <v>27.04</v>
       </c>
-      <c r="J21">
+      <c r="K21" s="1">
         <v>0.64</v>
       </c>
-      <c r="K21" s="1">
+      <c r="L21" s="1">
         <v>27.04</v>
       </c>
-      <c r="L21" t="s">
-        <v>74</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="M21" t="s">
+        <v>75</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F22">
         <v>35.58</v>
       </c>
       <c r="G22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H22">
-        <v>1.65</v>
+        <v>1.619</v>
       </c>
       <c r="I22" s="1">
-        <v>58.71</v>
+        <v>1.649</v>
       </c>
       <c r="J22">
+        <v>58.67142</v>
+      </c>
+      <c r="K22" s="1">
         <v>1.74</v>
       </c>
-      <c r="K22" s="1">
-        <v>61.91</v>
-      </c>
-      <c r="L22" t="s">
-        <v>75</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="L22" s="1">
+        <v>61.9092</v>
+      </c>
+      <c r="M22" t="s">
+        <v>76</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F23">
-        <v>53.05</v>
+        <v>53.047</v>
       </c>
       <c r="G23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H23">
         <v>0.64</v>
       </c>
       <c r="I23" s="1">
-        <v>33.95</v>
+        <v>0.64</v>
       </c>
       <c r="J23">
+        <v>33.95008</v>
+      </c>
+      <c r="K23" s="1">
         <v>0.64</v>
       </c>
-      <c r="K23" s="1">
-        <v>33.95</v>
-      </c>
-      <c r="L23" t="s">
-        <v>76</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="L23" s="1">
+        <v>33.95008</v>
+      </c>
+      <c r="M23" t="s">
+        <v>77</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F24">
-        <v>45.48</v>
+        <v>45.484</v>
       </c>
       <c r="G24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H24">
         <v>0.64</v>
       </c>
       <c r="I24" s="1">
-        <v>29.11</v>
+        <v>0.64</v>
       </c>
       <c r="J24">
+        <v>29.10976</v>
+      </c>
+      <c r="K24" s="1">
         <v>0.64</v>
       </c>
-      <c r="K24" s="1">
-        <v>29.11</v>
-      </c>
-      <c r="L24" t="s">
-        <v>77</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="N24" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="L24" s="1">
+        <v>29.10976</v>
+      </c>
+      <c r="M24" t="s">
+        <v>78</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F25">
         <v>42.18</v>
       </c>
       <c r="G25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H25">
-        <v>1.7</v>
+        <v>1.674</v>
       </c>
       <c r="I25" s="1">
-        <v>71.70999999999999</v>
+        <v>1.704</v>
       </c>
       <c r="J25">
+        <v>71.87472</v>
+      </c>
+      <c r="K25" s="1">
         <v>1.78</v>
       </c>
-      <c r="K25" s="1">
-        <v>75.08</v>
-      </c>
-      <c r="L25" t="s">
-        <v>78</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="L25" s="1">
+        <v>75.0804</v>
+      </c>
+      <c r="M25" t="s">
+        <v>79</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E26" t="s">
+        <v>55</v>
+      </c>
+      <c r="F26">
+        <v>41.401</v>
+      </c>
+      <c r="G26" t="s">
+        <v>57</v>
+      </c>
+      <c r="H26">
+        <v>1.674</v>
+      </c>
+      <c r="I26" s="1">
+        <v>1.704</v>
+      </c>
+      <c r="J26">
+        <v>70.547304</v>
+      </c>
+      <c r="K26" s="1">
+        <v>1.77</v>
+      </c>
+      <c r="L26" s="1">
+        <v>73.27977</v>
+      </c>
+      <c r="M26" t="s">
+        <v>80</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" t="s">
+        <v>47</v>
+      </c>
+      <c r="E27" t="s">
         <v>54</v>
       </c>
-      <c r="F26">
-        <v>41.4</v>
-      </c>
-      <c r="G26" t="s">
-        <v>56</v>
-      </c>
-      <c r="H26">
-        <v>1.7</v>
-      </c>
-      <c r="I26" s="1">
-        <v>70.38</v>
-      </c>
-      <c r="J26">
-        <v>1.77</v>
-      </c>
-      <c r="K26" s="1">
-        <v>73.28</v>
-      </c>
-      <c r="L26" t="s">
-        <v>79</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-      <c r="N26" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
-      <c r="A27" t="s">
-        <v>33</v>
-      </c>
-      <c r="B27" t="s">
-        <v>34</v>
-      </c>
-      <c r="C27" t="s">
-        <v>39</v>
-      </c>
-      <c r="D27" t="s">
-        <v>46</v>
-      </c>
-      <c r="E27" t="s">
-        <v>53</v>
-      </c>
       <c r="F27">
-        <v>43.73</v>
+        <v>43.734</v>
       </c>
       <c r="G27" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H27">
         <v>0.64</v>
       </c>
       <c r="I27" s="1">
-        <v>27.99</v>
+        <v>0.64</v>
       </c>
       <c r="J27">
+        <v>27.98976</v>
+      </c>
+      <c r="K27" s="1">
         <v>0.64</v>
       </c>
-      <c r="K27" s="1">
-        <v>27.99</v>
-      </c>
-      <c r="L27" t="s">
-        <v>80</v>
-      </c>
-      <c r="M27">
-        <v>0</v>
-      </c>
-      <c r="N27" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
+      <c r="L27" s="1">
+        <v>27.98976</v>
+      </c>
+      <c r="M27" t="s">
+        <v>81</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C28" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D28" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F28">
-        <v>48.27</v>
+        <v>48.266</v>
       </c>
       <c r="G28" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H28">
         <v>0.64</v>
       </c>
       <c r="I28" s="1">
-        <v>30.89</v>
+        <v>0.64</v>
       </c>
       <c r="J28">
+        <v>30.89024</v>
+      </c>
+      <c r="K28" s="1">
         <v>0.64</v>
       </c>
-      <c r="K28" s="1">
-        <v>30.89</v>
-      </c>
-      <c r="L28" t="s">
-        <v>81</v>
-      </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
-      <c r="N28" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
+      <c r="L28" s="1">
+        <v>30.89024</v>
+      </c>
+      <c r="M28" t="s">
+        <v>82</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
       <c r="A31" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -2016,38 +2103,38 @@
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:15">
       <c r="A32" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B33" s="6">
-        <v>697.67</v>
+        <v>697.662</v>
       </c>
       <c r="C33" s="6">
         <v>16</v>
       </c>
       <c r="D33" s="7">
-        <v>0.639027</v>
+        <v>0.639035</v>
       </c>
       <c r="E33" s="6">
         <v>445.83</v>
@@ -2058,19 +2145,19 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B34" s="6">
-        <v>394.9</v>
+        <v>394.904</v>
       </c>
       <c r="C34" s="6">
         <v>10</v>
       </c>
       <c r="D34" s="7">
-        <v>1.567587</v>
+        <v>1.568956</v>
       </c>
       <c r="E34" s="6">
-        <v>619.04</v>
+        <v>619.59</v>
       </c>
       <c r="F34" s="6">
         <v>656.85</v>
@@ -2078,19 +2165,19 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B35" s="6">
-        <v>26.14</v>
+        <v>26.137</v>
       </c>
       <c r="C35" s="6">
         <v>1</v>
       </c>
       <c r="D35" s="7">
-        <v>1.400153</v>
+        <v>1.399</v>
       </c>
       <c r="E35" s="6">
-        <v>36.6</v>
+        <v>36.57</v>
       </c>
       <c r="F35" s="6">
         <v>39.99</v>
@@ -2098,17 +2185,17 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B36" s="9">
-        <v>1118.71</v>
+        <v>1118.703</v>
       </c>
       <c r="C36" s="9">
         <v>27</v>
       </c>
       <c r="D36" s="7"/>
       <c r="E36" s="9">
-        <v>1101.47</v>
+        <v>1101.99</v>
       </c>
       <c r="F36" s="9">
         <v>1142.67</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СКИМПРОТ ООД % ГРУПА 2/СКИМПРОТ ООД % ГРУПА 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СКИМПРОТ ООД % ГРУПА 2/СКИМПРОТ ООД % ГРУПА 2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="114">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -366,8 +363,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -460,10 +457,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -758,7 +755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O36"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -771,13 +768,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -820,1282 +817,1198 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F2">
         <v>26.364</v>
       </c>
       <c r="G2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H2">
         <v>0.66</v>
       </c>
       <c r="I2" s="1">
+        <v>17.4</v>
+      </c>
+      <c r="J2">
         <v>0.66</v>
       </c>
-      <c r="J2">
-        <v>17.40024</v>
-      </c>
       <c r="K2" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="L2" s="1">
-        <v>17.40024</v>
-      </c>
-      <c r="M2" t="s">
-        <v>58</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>17.4</v>
+      </c>
+      <c r="L2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F3">
         <v>39.848</v>
       </c>
       <c r="G3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H3">
         <v>0.66</v>
       </c>
       <c r="I3" s="1">
+        <v>26.3</v>
+      </c>
+      <c r="J3">
         <v>0.66</v>
       </c>
-      <c r="J3">
-        <v>26.29968</v>
-      </c>
       <c r="K3" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="L3" s="1">
-        <v>26.29968</v>
-      </c>
-      <c r="M3" t="s">
-        <v>59</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>26.3</v>
+      </c>
+      <c r="L3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F4">
         <v>52.569</v>
       </c>
       <c r="G4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H4">
         <v>0.65</v>
       </c>
       <c r="I4" s="1">
+        <v>34.17</v>
+      </c>
+      <c r="J4">
         <v>0.65</v>
       </c>
-      <c r="J4">
-        <v>34.16985</v>
-      </c>
       <c r="K4" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="L4" s="1">
-        <v>34.16985</v>
-      </c>
-      <c r="M4" t="s">
-        <v>60</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>34.17</v>
+      </c>
+      <c r="L4" t="s">
+        <v>59</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F5">
         <v>47.46</v>
       </c>
       <c r="G5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H5">
         <v>0.63</v>
       </c>
       <c r="I5" s="1">
+        <v>29.9</v>
+      </c>
+      <c r="J5">
         <v>0.63</v>
       </c>
-      <c r="J5">
-        <v>29.8998</v>
-      </c>
       <c r="K5" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="L5" s="1">
-        <v>29.8998</v>
-      </c>
-      <c r="M5" t="s">
-        <v>61</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>29.9</v>
+      </c>
+      <c r="L5" t="s">
+        <v>60</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F6">
         <v>41.81</v>
       </c>
       <c r="G6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H6">
         <v>0.63</v>
       </c>
       <c r="I6" s="1">
+        <v>26.34</v>
+      </c>
+      <c r="J6">
         <v>0.63</v>
       </c>
-      <c r="J6">
-        <v>26.3403</v>
-      </c>
       <c r="K6" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="L6" s="1">
-        <v>26.3403</v>
-      </c>
-      <c r="M6" t="s">
-        <v>62</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>26.34</v>
+      </c>
+      <c r="L6" t="s">
+        <v>61</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F7">
         <v>42.127</v>
       </c>
       <c r="G7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H7">
         <v>0.63</v>
       </c>
       <c r="I7" s="1">
+        <v>26.54</v>
+      </c>
+      <c r="J7">
         <v>0.63</v>
       </c>
-      <c r="J7">
-        <v>26.54001</v>
-      </c>
       <c r="K7" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="L7" s="1">
-        <v>26.54001</v>
-      </c>
-      <c r="M7" t="s">
-        <v>63</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>26.54</v>
+      </c>
+      <c r="L7" t="s">
+        <v>62</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F8">
         <v>37.71</v>
       </c>
       <c r="G8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H8">
-        <v>1.412</v>
+        <v>1.442</v>
       </c>
       <c r="I8" s="1">
-        <v>1.442</v>
+        <v>54.378</v>
       </c>
       <c r="J8">
-        <v>54.37782</v>
+        <v>1.55</v>
       </c>
       <c r="K8" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L8" s="1">
-        <v>58.4505</v>
-      </c>
-      <c r="M8" t="s">
-        <v>64</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>58.451</v>
+      </c>
+      <c r="L8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F9">
         <v>38.948</v>
       </c>
       <c r="G9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H9">
-        <v>1.412</v>
+        <v>1.442</v>
       </c>
       <c r="I9" s="1">
-        <v>1.442</v>
+        <v>56.163</v>
       </c>
       <c r="J9">
-        <v>56.163016</v>
+        <v>1.55</v>
       </c>
       <c r="K9" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L9" s="1">
-        <v>60.3694</v>
-      </c>
-      <c r="M9" t="s">
-        <v>65</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>60.369</v>
+      </c>
+      <c r="L9" t="s">
+        <v>64</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F10">
         <v>44.286</v>
       </c>
       <c r="G10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H10">
         <v>0.63</v>
       </c>
       <c r="I10" s="1">
+        <v>27.9</v>
+      </c>
+      <c r="J10">
         <v>0.63</v>
       </c>
-      <c r="J10">
-        <v>27.90018</v>
-      </c>
       <c r="K10" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="L10" s="1">
-        <v>27.90018</v>
-      </c>
-      <c r="M10" t="s">
-        <v>66</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>27.9</v>
+      </c>
+      <c r="L10" t="s">
+        <v>65</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F11">
         <v>38.911</v>
       </c>
       <c r="G11" t="s">
+        <v>56</v>
+      </c>
+      <c r="H11">
+        <v>1.481</v>
+      </c>
+      <c r="I11" s="1">
+        <v>57.627</v>
+      </c>
+      <c r="J11">
+        <v>1.58</v>
+      </c>
+      <c r="K11" s="1">
+        <v>61.479</v>
+      </c>
+      <c r="L11" t="s">
         <v>57</v>
       </c>
-      <c r="H11">
-        <v>1.451</v>
-      </c>
-      <c r="I11" s="1">
-        <v>1.481</v>
-      </c>
-      <c r="J11">
-        <v>57.627191</v>
-      </c>
-      <c r="K11" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="L11" s="1">
-        <v>61.47938</v>
-      </c>
-      <c r="M11" t="s">
-        <v>58</v>
-      </c>
-      <c r="N11">
+      <c r="M11">
         <v>187547</v>
       </c>
-      <c r="O11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="N11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F12">
         <v>29.981</v>
       </c>
       <c r="G12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H12">
-        <v>1.451</v>
+        <v>1.481</v>
       </c>
       <c r="I12" s="1">
-        <v>1.481</v>
+        <v>44.402</v>
       </c>
       <c r="J12">
-        <v>44.401861</v>
+        <v>1.58</v>
       </c>
       <c r="K12" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="L12" s="1">
-        <v>47.36998</v>
-      </c>
-      <c r="M12" t="s">
-        <v>67</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>47.37</v>
+      </c>
+      <c r="L12" t="s">
+        <v>66</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F13">
         <v>39.778</v>
       </c>
       <c r="G13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H13">
         <v>0.63</v>
       </c>
       <c r="I13" s="1">
+        <v>25.06</v>
+      </c>
+      <c r="J13">
         <v>0.63</v>
       </c>
-      <c r="J13">
-        <v>25.06014</v>
-      </c>
       <c r="K13" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="L13" s="1">
-        <v>25.06014</v>
-      </c>
-      <c r="M13" t="s">
-        <v>68</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>25.06</v>
+      </c>
+      <c r="L13" t="s">
+        <v>67</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F14">
         <v>36.889</v>
       </c>
       <c r="G14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H14">
         <v>0.63</v>
       </c>
       <c r="I14" s="1">
+        <v>23.24</v>
+      </c>
+      <c r="J14">
         <v>0.63</v>
       </c>
-      <c r="J14">
-        <v>23.24007</v>
-      </c>
       <c r="K14" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="L14" s="1">
-        <v>23.24007</v>
-      </c>
-      <c r="M14" t="s">
-        <v>69</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>23.24</v>
+      </c>
+      <c r="L14" t="s">
+        <v>68</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F15">
         <v>41.852</v>
       </c>
       <c r="G15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H15">
-        <v>1.499</v>
+        <v>1.529</v>
       </c>
       <c r="I15" s="1">
-        <v>1.529</v>
+        <v>63.992</v>
       </c>
       <c r="J15">
-        <v>63.991708</v>
+        <v>1.62</v>
       </c>
       <c r="K15" s="1">
-        <v>1.62</v>
-      </c>
-      <c r="L15" s="1">
-        <v>67.80024</v>
-      </c>
-      <c r="M15" t="s">
-        <v>70</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>67.8</v>
+      </c>
+      <c r="L15" t="s">
+        <v>69</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F16">
         <v>26.137</v>
       </c>
       <c r="G16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H16">
-        <v>1.369</v>
+        <v>1.399</v>
       </c>
       <c r="I16" s="1">
-        <v>1.399</v>
+        <v>36.566</v>
       </c>
       <c r="J16">
-        <v>36.565663</v>
+        <v>1.53</v>
       </c>
       <c r="K16" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="L16" s="1">
-        <v>39.98961</v>
-      </c>
-      <c r="M16" t="s">
-        <v>71</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+        <v>39.99</v>
+      </c>
+      <c r="L16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F17">
         <v>53.484</v>
       </c>
       <c r="G17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H17">
         <v>0.64</v>
       </c>
       <c r="I17" s="1">
+        <v>34.23</v>
+      </c>
+      <c r="J17">
         <v>0.64</v>
       </c>
-      <c r="J17">
-        <v>34.22976</v>
-      </c>
       <c r="K17" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L17" s="1">
-        <v>34.22976</v>
-      </c>
-      <c r="M17" t="s">
-        <v>71</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+        <v>34.23</v>
+      </c>
+      <c r="L17" t="s">
+        <v>70</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F18">
         <v>41.829</v>
       </c>
       <c r="G18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H18">
-        <v>1.564</v>
+        <v>1.594</v>
       </c>
       <c r="I18" s="1">
-        <v>1.594</v>
+        <v>66.675</v>
       </c>
       <c r="J18">
-        <v>66.675426</v>
+        <v>1.7</v>
       </c>
       <c r="K18" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L18" s="1">
-        <v>71.1093</v>
-      </c>
-      <c r="M18" t="s">
-        <v>72</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+        <v>71.10899999999999</v>
+      </c>
+      <c r="L18" t="s">
+        <v>71</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F19">
         <v>40.266</v>
       </c>
       <c r="G19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H19">
         <v>0.64</v>
       </c>
       <c r="I19" s="1">
+        <v>25.77</v>
+      </c>
+      <c r="J19">
         <v>0.64</v>
       </c>
-      <c r="J19">
-        <v>25.77024</v>
-      </c>
       <c r="K19" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L19" s="1">
-        <v>25.77024</v>
-      </c>
-      <c r="M19" t="s">
-        <v>73</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
+        <v>25.77</v>
+      </c>
+      <c r="L19" t="s">
+        <v>72</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F20">
         <v>46.512</v>
       </c>
       <c r="G20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H20">
-        <v>1.588</v>
+        <v>1.618</v>
       </c>
       <c r="I20" s="1">
-        <v>1.618</v>
+        <v>75.256</v>
       </c>
       <c r="J20">
-        <v>75.256416</v>
+        <v>1.72</v>
       </c>
       <c r="K20" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L20" s="1">
-        <v>80.00064</v>
-      </c>
-      <c r="M20" t="s">
-        <v>74</v>
-      </c>
-      <c r="N20">
+        <v>80.001</v>
+      </c>
+      <c r="L20" t="s">
+        <v>73</v>
+      </c>
+      <c r="M20">
         <v>209590</v>
       </c>
-      <c r="O20" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
+      <c r="N20" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F21">
         <v>42.25</v>
       </c>
       <c r="G21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H21">
         <v>0.64</v>
       </c>
       <c r="I21" s="1">
+        <v>27.04</v>
+      </c>
+      <c r="J21">
         <v>0.64</v>
       </c>
-      <c r="J21">
+      <c r="K21" s="1">
         <v>27.04</v>
       </c>
-      <c r="K21" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L21" s="1">
-        <v>27.04</v>
-      </c>
-      <c r="M21" t="s">
-        <v>75</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
+      <c r="L21" t="s">
+        <v>74</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F22">
         <v>35.58</v>
       </c>
       <c r="G22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H22">
-        <v>1.619</v>
+        <v>1.649</v>
       </c>
       <c r="I22" s="1">
-        <v>1.649</v>
+        <v>58.671</v>
       </c>
       <c r="J22">
-        <v>58.67142</v>
+        <v>1.74</v>
       </c>
       <c r="K22" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="L22" s="1">
-        <v>61.9092</v>
-      </c>
-      <c r="M22" t="s">
-        <v>76</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
+        <v>61.909</v>
+      </c>
+      <c r="L22" t="s">
+        <v>75</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E23" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F23">
         <v>53.047</v>
       </c>
       <c r="G23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H23">
         <v>0.64</v>
       </c>
       <c r="I23" s="1">
+        <v>33.95</v>
+      </c>
+      <c r="J23">
         <v>0.64</v>
       </c>
-      <c r="J23">
-        <v>33.95008</v>
-      </c>
       <c r="K23" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L23" s="1">
-        <v>33.95008</v>
-      </c>
-      <c r="M23" t="s">
-        <v>77</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+        <v>33.95</v>
+      </c>
+      <c r="L23" t="s">
+        <v>76</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E24" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F24">
         <v>45.484</v>
       </c>
       <c r="G24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H24">
         <v>0.64</v>
       </c>
       <c r="I24" s="1">
+        <v>29.11</v>
+      </c>
+      <c r="J24">
         <v>0.64</v>
       </c>
-      <c r="J24">
-        <v>29.10976</v>
-      </c>
       <c r="K24" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L24" s="1">
-        <v>29.10976</v>
-      </c>
-      <c r="M24" t="s">
-        <v>78</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
+        <v>29.11</v>
+      </c>
+      <c r="L24" t="s">
+        <v>77</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F25">
         <v>42.18</v>
       </c>
       <c r="G25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H25">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I25" s="1">
-        <v>1.704</v>
+        <v>71.875</v>
       </c>
       <c r="J25">
-        <v>71.87472</v>
+        <v>1.78</v>
       </c>
       <c r="K25" s="1">
-        <v>1.78</v>
-      </c>
-      <c r="L25" s="1">
-        <v>75.0804</v>
-      </c>
-      <c r="M25" t="s">
-        <v>79</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
+        <v>75.08</v>
+      </c>
+      <c r="L25" t="s">
+        <v>78</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F26">
         <v>41.401</v>
       </c>
       <c r="G26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H26">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I26" s="1">
-        <v>1.704</v>
+        <v>70.547</v>
       </c>
       <c r="J26">
-        <v>70.547304</v>
+        <v>1.77</v>
       </c>
       <c r="K26" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L26" s="1">
-        <v>73.27977</v>
-      </c>
-      <c r="M26" t="s">
-        <v>80</v>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
+        <v>73.28</v>
+      </c>
+      <c r="L26" t="s">
+        <v>79</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" t="s">
         <v>34</v>
       </c>
-      <c r="B27" t="s">
-        <v>35</v>
-      </c>
       <c r="C27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F27">
         <v>43.734</v>
       </c>
       <c r="G27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H27">
         <v>0.64</v>
       </c>
       <c r="I27" s="1">
+        <v>27.99</v>
+      </c>
+      <c r="J27">
         <v>0.64</v>
       </c>
-      <c r="J27">
-        <v>27.98976</v>
-      </c>
       <c r="K27" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L27" s="1">
-        <v>27.98976</v>
-      </c>
-      <c r="M27" t="s">
-        <v>81</v>
-      </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15">
+        <v>27.99</v>
+      </c>
+      <c r="L27" t="s">
+        <v>80</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" t="s">
         <v>34</v>
       </c>
-      <c r="B28" t="s">
-        <v>35</v>
-      </c>
       <c r="C28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F28">
         <v>48.266</v>
       </c>
       <c r="G28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H28">
         <v>0.64</v>
       </c>
       <c r="I28" s="1">
+        <v>30.89</v>
+      </c>
+      <c r="J28">
         <v>0.64</v>
       </c>
-      <c r="J28">
-        <v>30.89024</v>
-      </c>
       <c r="K28" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L28" s="1">
-        <v>30.89024</v>
-      </c>
-      <c r="M28" t="s">
-        <v>82</v>
-      </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28" t="s">
+        <v>30.89</v>
+      </c>
+      <c r="L28" t="s">
+        <v>81</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="3" t="s">
         <v>108</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15">
-      <c r="A31" s="3" t="s">
-        <v>109</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -2103,89 +2016,89 @@
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
     </row>
-    <row r="32" spans="1:15">
+    <row r="32" spans="1:14">
       <c r="A32" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="C32" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="D32" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D32" s="4" t="s">
-        <v>113</v>
-      </c>
       <c r="E32" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B33" s="6">
         <v>697.662</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="7">
         <v>16</v>
       </c>
       <c r="D33" s="7">
-        <v>0.639035</v>
-      </c>
-      <c r="E33" s="6">
+        <v>0.639</v>
+      </c>
+      <c r="E33" s="7">
         <v>445.83</v>
       </c>
-      <c r="F33" s="6">
+      <c r="F33" s="7">
         <v>445.83</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B34" s="6">
         <v>394.904</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C34" s="7">
         <v>10</v>
       </c>
       <c r="D34" s="7">
-        <v>1.568956</v>
-      </c>
-      <c r="E34" s="6">
-        <v>619.59</v>
-      </c>
-      <c r="F34" s="6">
-        <v>656.85</v>
+        <v>1.569</v>
+      </c>
+      <c r="E34" s="7">
+        <v>619.586</v>
+      </c>
+      <c r="F34" s="7">
+        <v>656.848</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B35" s="6">
         <v>26.137</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="7">
         <v>1</v>
       </c>
       <c r="D35" s="7">
         <v>1.399</v>
       </c>
-      <c r="E35" s="6">
-        <v>36.57</v>
-      </c>
-      <c r="F35" s="6">
+      <c r="E35" s="7">
+        <v>36.566</v>
+      </c>
+      <c r="F35" s="7">
         <v>39.99</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B36" s="9">
         <v>1118.703</v>
@@ -2195,10 +2108,10 @@
       </c>
       <c r="D36" s="7"/>
       <c r="E36" s="9">
-        <v>1101.99</v>
+        <v>1101.982</v>
       </c>
       <c r="F36" s="9">
-        <v>1142.67</v>
+        <v>1142.668</v>
       </c>
     </row>
   </sheetData>
